--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>29.7522</v>
+        <v>32.6496</v>
       </c>
       <c r="E2" t="n">
-        <v>14.382</v>
+        <v>16.7621</v>
       </c>
       <c r="F2" t="n">
-        <v>15.3705</v>
+        <v>15.8874</v>
       </c>
       <c r="G2" t="n">
-        <v>23.7375</v>
+        <v>27.4549</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5951</v>
+        <v>1.0862</v>
       </c>
       <c r="I2" t="n">
-        <v>22.1421</v>
+        <v>26.3687</v>
       </c>
       <c r="J2" t="n">
-        <v>20.0325</v>
+        <v>23.2126</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6389999999999998</v>
+        <v>-0.1869999999999998</v>
       </c>
       <c r="L2" t="n">
-        <v>19.3938</v>
+        <v>23.3996</v>
       </c>
       <c r="M2" t="n">
-        <v>3.705</v>
+        <v>4.2424</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9564000000000001</v>
+        <v>1.2735</v>
       </c>
       <c r="O2" t="n">
-        <v>2.748</v>
+        <v>2.9692</v>
       </c>
       <c r="P2" t="n">
-        <v>3.4614</v>
+        <v>4.8964</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.9228</v>
+        <v>-6.9948</v>
       </c>
       <c r="R2" t="n">
-        <v>10.3839</v>
+        <v>11.8915</v>
       </c>
       <c r="S2" t="n">
-        <v>4.608000000000001</v>
+        <v>3.3782</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4492</v>
+        <v>1.7336</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1588</v>
+        <v>1.6447</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.0541</v>
+        <v>-3.0803</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.1769</v>
+        <v>-1.1892</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8772</v>
+        <v>-1.8911</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>22.8177</v>
+        <v>20.8653</v>
       </c>
       <c r="E3" t="n">
-        <v>17.1321</v>
+        <v>17.2959</v>
       </c>
       <c r="F3" t="n">
-        <v>5.685899999999999</v>
+        <v>3.5693</v>
       </c>
       <c r="G3" t="n">
-        <v>7.283100000000001</v>
+        <v>5.760999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-9.9741</v>
+        <v>-11.1274</v>
       </c>
       <c r="I3" t="n">
-        <v>17.2572</v>
+        <v>16.8884</v>
       </c>
       <c r="J3" t="n">
-        <v>13.1115</v>
+        <v>14.936</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.7999</v>
+        <v>-5.142499999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>18.9111</v>
+        <v>20.0786</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.8284</v>
+        <v>-9.174700000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.1736</v>
+        <v>-5.9845</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6545</v>
+        <v>-3.1902</v>
       </c>
       <c r="P3" t="n">
-        <v>8.999700000000001</v>
+        <v>8.393799999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-11.0763</v>
+        <v>-13.5235</v>
       </c>
       <c r="R3" t="n">
-        <v>20.0754</v>
+        <v>21.9179</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8118</v>
+        <v>-0.2585</v>
       </c>
       <c r="T3" t="n">
-        <v>4.527</v>
+        <v>3.9747</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.7152</v>
+        <v>-4.2332</v>
       </c>
       <c r="V3" t="n">
-        <v>5.7237</v>
+        <v>6.9684</v>
       </c>
       <c r="W3" t="n">
-        <v>10.5702</v>
+        <v>11.909</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.8465</v>
+        <v>-4.9403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>16.4466</v>
+        <v>14.9883</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.421100000000001</v>
+        <v>6.3898</v>
       </c>
       <c r="F4" t="n">
-        <v>23.8674</v>
+        <v>8.5982</v>
       </c>
       <c r="G4" t="n">
-        <v>7.626</v>
+        <v>10.8076</v>
       </c>
       <c r="H4" t="n">
-        <v>4.206</v>
+        <v>3.0172</v>
       </c>
       <c r="I4" t="n">
-        <v>3.42</v>
+        <v>7.790100000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0434</v>
+        <v>9.648199999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>4.816800000000001</v>
+        <v>7.5387</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.7737</v>
+        <v>2.1095</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5829</v>
+        <v>1.1593</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6107999999999998</v>
+        <v>-4.5213</v>
       </c>
       <c r="O4" t="n">
-        <v>7.1931</v>
+        <v>5.6806</v>
       </c>
       <c r="P4" t="n">
-        <v>5.5383</v>
+        <v>-2.5649</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.8453</v>
+        <v>-22.8507</v>
       </c>
       <c r="R4" t="n">
-        <v>19.3836</v>
+        <v>20.2855</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4051</v>
+        <v>-4.888699999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>4.0647</v>
+        <v>0.9740000000000002</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.6599</v>
+        <v>-5.8627</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8772</v>
+        <v>11.6341</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3158</v>
+        <v>18.6181</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4386</v>
+        <v>-6.9837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>11.7702</v>
+        <v>13.9367</v>
       </c>
       <c r="E5" t="n">
-        <v>4.061999999999999</v>
+        <v>-9.2925</v>
       </c>
       <c r="F5" t="n">
-        <v>7.7079</v>
+        <v>23.2292</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2994</v>
+        <v>8.466699999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-12.0696</v>
+        <v>2.746</v>
       </c>
       <c r="I5" t="n">
-        <v>11.7702</v>
+        <v>5.7207</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4383</v>
+        <v>2.5921</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.9651</v>
+        <v>4.4034</v>
       </c>
       <c r="L5" t="n">
-        <v>9.5265</v>
+        <v>-1.8116</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1392000000000002</v>
+        <v>5.874899999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1045</v>
+        <v>-1.6577</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2437</v>
+        <v>7.5323</v>
       </c>
       <c r="P5" t="n">
-        <v>10.3842</v>
+        <v>3.4977</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.153799999999999</v>
+        <v>-17.4874</v>
       </c>
       <c r="R5" t="n">
-        <v>14.5374</v>
+        <v>20.9851</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1067</v>
+        <v>1.1488</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1382999999999998</v>
+        <v>3.3004</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2447</v>
+        <v>-2.1516</v>
       </c>
       <c r="V5" t="n">
-        <v>2.7924</v>
+        <v>0.8234999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>8.5161</v>
+        <v>2.3027</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.7237</v>
+        <v>-1.4792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>11.5245</v>
+        <v>13.8992</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1408</v>
+        <v>7.520300000000002</v>
       </c>
       <c r="F6" t="n">
-        <v>9.3834</v>
+        <v>6.3785</v>
       </c>
       <c r="G6" t="n">
-        <v>8.3352</v>
+        <v>1.082500000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5792</v>
+        <v>-10.7443</v>
       </c>
       <c r="I6" t="n">
-        <v>6.7557</v>
+        <v>11.8268</v>
       </c>
       <c r="J6" t="n">
-        <v>5.286</v>
+        <v>2.965</v>
       </c>
       <c r="K6" t="n">
-        <v>4.209</v>
+        <v>-7.5284</v>
       </c>
       <c r="L6" t="n">
-        <v>1.077</v>
+        <v>10.4934</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0492</v>
+        <v>-1.8822</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6298</v>
+        <v>-3.2158</v>
       </c>
       <c r="O6" t="n">
-        <v>5.679</v>
+        <v>1.3334</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.769</v>
+        <v>11.8915</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.4599</v>
+        <v>-4.197</v>
       </c>
       <c r="R6" t="n">
-        <v>18.6912</v>
+        <v>16.0882</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.6116</v>
+        <v>-0.7975</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1442</v>
+        <v>0.3361000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.7558</v>
+        <v>-1.1337</v>
       </c>
       <c r="V6" t="n">
-        <v>10.5702</v>
+        <v>1.723</v>
       </c>
       <c r="W6" t="n">
-        <v>17.1711</v>
+        <v>8.4171</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.600899999999999</v>
+        <v>-6.6938</v>
       </c>
     </row>
     <row r="7">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8377</v>
+        <v>3.5872</v>
       </c>
       <c r="E7" t="n">
-        <v>7.4607</v>
+        <v>4.307</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6227</v>
+        <v>-0.7201000000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>7.3845</v>
+        <v>6.839600000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.385900000000001</v>
+        <v>1.0669</v>
       </c>
       <c r="I7" t="n">
-        <v>4.998900000000001</v>
+        <v>5.7723</v>
       </c>
       <c r="J7" t="n">
-        <v>3.254700000000001</v>
+        <v>2.364099999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6224999999999997</v>
+        <v>-1.6713</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8769</v>
+        <v>4.0351</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1301</v>
+        <v>4.4754</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0084</v>
+        <v>2.7382</v>
       </c>
       <c r="O7" t="n">
-        <v>1.122</v>
+        <v>1.7372</v>
       </c>
       <c r="P7" t="n">
-        <v>8.3073</v>
+        <v>6.7618</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6924</v>
+        <v>-3.0313</v>
       </c>
       <c r="R7" t="n">
-        <v>8.999700000000001</v>
+        <v>9.793100000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2775</v>
+        <v>0.004000000000000059</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7902000000000001</v>
+        <v>0.9488</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5124000000000001</v>
+        <v>-0.9447999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-10.1316</v>
+        <v>-10.0176</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1082</v>
+        <v>4.0257</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.2398</v>
+        <v>-14.0433</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3239</v>
+        <v>-2.4322</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.799300000000001</v>
+        <v>-4.869800000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4751</v>
+        <v>2.4367</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1302</v>
+        <v>1.7014</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.8951</v>
+        <v>2.1461</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7646</v>
+        <v>-0.4446999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.485300000000001</v>
+        <v>-0.4047999999999998</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2081999999999996</v>
+        <v>0.2441</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6938</v>
+        <v>-0.6486000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.6158</v>
+        <v>2.1065</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.686599999999999</v>
+        <v>1.9026</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0711</v>
+        <v>0.2042</v>
       </c>
       <c r="P8" t="n">
-        <v>5.5383</v>
+        <v>-2.5649</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.3842</v>
+        <v>-6.9948</v>
       </c>
       <c r="R8" t="n">
-        <v>15.9219</v>
+        <v>4.4302</v>
       </c>
       <c r="S8" t="n">
-        <v>5.0838</v>
+        <v>-3.3985</v>
       </c>
       <c r="T8" t="n">
-        <v>5.4531</v>
+        <v>-0.6714</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3693000000000001</v>
+        <v>-2.727</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.8155</v>
+        <v>1.829199999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-2.3538</v>
+        <v>3.2019</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.462</v>
+        <v>-1.3727</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1032</v>
+        <v>-5.1343</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2599</v>
+        <v>-5.3757</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1564</v>
+        <v>0.2413999999999996</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1874</v>
+        <v>-5.428199999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2584</v>
+        <v>-12.6518</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0713</v>
+        <v>7.223599999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0131</v>
+        <v>2.6133</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2685</v>
+        <v>-2.9292</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2816</v>
+        <v>5.5425</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1999</v>
+        <v>-8.041</v>
       </c>
       <c r="N9" t="n">
-        <v>1.9896</v>
+        <v>-9.722300000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2103</v>
+        <v>1.6811</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.769</v>
+        <v>6.5286</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.9228</v>
+        <v>-11.658</v>
       </c>
       <c r="R9" t="n">
-        <v>4.153799999999999</v>
+        <v>18.1869</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.4365</v>
+        <v>3.7518</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5553</v>
+        <v>4.9804</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.8812</v>
+        <v>-1.2285</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9152</v>
+        <v>-9.986800000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>3.231</v>
+        <v>-1.3111</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3158</v>
+        <v>-8.675699999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.564599999999999</v>
+        <v>-7.067499999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0532</v>
+        <v>-2.760600000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5111</v>
+        <v>-4.3066</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.888100000000001</v>
+        <v>-10.6156</v>
       </c>
       <c r="H10" t="n">
-        <v>-14.1477</v>
+        <v>-16.8692</v>
       </c>
       <c r="I10" t="n">
-        <v>5.259600000000001</v>
+        <v>6.2536</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.116900000000001</v>
+        <v>-8.6922</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.5448</v>
+        <v>-15.0015</v>
       </c>
       <c r="L10" t="n">
-        <v>5.427899999999999</v>
+        <v>6.3096</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7709</v>
+        <v>-1.9231</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6026</v>
+        <v>-1.8674</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1683000000000001</v>
+        <v>-0.05630000000000006</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6921000000000004</v>
+        <v>0.6996</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.3839</v>
+        <v>-11.6583</v>
       </c>
       <c r="R10" t="n">
-        <v>11.0763</v>
+        <v>12.3576</v>
       </c>
       <c r="S10" t="n">
-        <v>15.4317</v>
+        <v>15.5498</v>
       </c>
       <c r="T10" t="n">
-        <v>15.4479</v>
+        <v>15.455</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.01560000000000061</v>
+        <v>0.09509999999999974</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.8009</v>
+        <v>-12.7017</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1347</v>
       </c>
       <c r="X10" t="n">
-        <v>-13.8009</v>
+        <v>-14.8363</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.0293</v>
+        <v>-11.6572</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.9258</v>
+        <v>-12.9209</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1037999999999997</v>
+        <v>1.2635</v>
       </c>
       <c r="G11" t="n">
-        <v>-13.8969</v>
+        <v>-7.2888</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.9973</v>
+        <v>0.7784999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.9002</v>
+        <v>-8.067600000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.9978</v>
+        <v>-4.9499</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3931</v>
+        <v>0.3440000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.605</v>
+        <v>-5.2939</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.8994</v>
+        <v>-2.3383</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.6042</v>
+        <v>0.4345000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.2952</v>
+        <v>-2.773</v>
       </c>
       <c r="P11" t="n">
-        <v>5.5383</v>
+        <v>3.497199999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.6152</v>
+        <v>-6.995100000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>13.1529</v>
+        <v>10.4923</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.178</v>
+        <v>-3.0629</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2486</v>
+        <v>-0.9756</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.426</v>
+        <v>-2.0876</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4927</v>
+        <v>-4.802999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4386</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9313</v>
+        <v>-4.802999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.2281</v>
+        <v>-14.8919</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.917</v>
+        <v>-12.3301</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3111</v>
+        <v>-2.561999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.6676</v>
+        <v>-15.4778</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2574</v>
+        <v>-6.6518</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.9253</v>
+        <v>-8.825699999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.4071</v>
+        <v>-6.1368</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1887000000000001</v>
+        <v>-1.8951</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.2187</v>
+        <v>-4.2417</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.260200000000001</v>
+        <v>-9.341000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4461000000000002</v>
+        <v>-4.7573</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.706</v>
+        <v>-4.584</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0766</v>
+        <v>6.762</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.9225</v>
+        <v>-7.6944</v>
       </c>
       <c r="R12" t="n">
-        <v>8.999400000000001</v>
+        <v>14.4564</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7906</v>
+        <v>-2.6842</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5871000000000002</v>
+        <v>1.0898</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2035</v>
+        <v>-3.7737</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.8465</v>
+        <v>-3.4919</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.4119</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.8465</v>
+        <v>-3.9038</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>59.8998</v>
+        <v>58.74319999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.198700000000002</v>
+        <v>4.725500000000013</v>
       </c>
       <c r="F13" t="n">
-        <v>62.0979</v>
+        <v>54.0155</v>
       </c>
       <c r="G13" t="n">
-        <v>20.6715</v>
+        <v>23.30329999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-37.8018</v>
+        <v>-47.2036</v>
       </c>
       <c r="I13" t="n">
-        <v>58.4715</v>
+        <v>70.50620000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>22.2402</v>
+        <v>38.1476</v>
       </c>
       <c r="K13" t="n">
-        <v>-21.789</v>
+        <v>-21.8248</v>
       </c>
       <c r="L13" t="n">
-        <v>44.02800000000001</v>
+        <v>59.9725</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.568400000000003</v>
+        <v>-14.8418</v>
       </c>
       <c r="N13" t="n">
-        <v>-16.0116</v>
+        <v>-25.3775</v>
       </c>
       <c r="O13" t="n">
-        <v>14.4432</v>
+        <v>10.5345</v>
       </c>
       <c r="P13" t="n">
-        <v>44.9982</v>
+        <v>47.7988</v>
       </c>
       <c r="Q13" t="n">
-        <v>-100.3791</v>
+        <v>-113.0853</v>
       </c>
       <c r="R13" t="n">
-        <v>145.3755</v>
+        <v>160.8847</v>
       </c>
       <c r="S13" t="n">
-        <v>14.4945</v>
+        <v>8.7423</v>
       </c>
       <c r="T13" t="n">
-        <v>34.1208</v>
+        <v>31.1458</v>
       </c>
       <c r="U13" t="n">
-        <v>-19.6248</v>
+        <v>-22.403</v>
       </c>
       <c r="V13" t="n">
-        <v>-20.2626</v>
+        <v>-21.1031</v>
       </c>
       <c r="W13" t="n">
-        <v>41.8203</v>
+        <v>48.5208</v>
       </c>
       <c r="X13" t="n">
-        <v>-62.08319999999999</v>
+        <v>-69.6229</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>32.6496</v>
+        <v>6.873699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7621</v>
+        <v>8.360500000000002</v>
       </c>
       <c r="F2" t="n">
-        <v>15.8874</v>
+        <v>-1.486699999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>27.4549</v>
+        <v>3.9147</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0862</v>
+        <v>-2.7681</v>
       </c>
       <c r="I2" t="n">
-        <v>26.3687</v>
+        <v>6.682999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>23.2126</v>
+        <v>9.920199999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1869999999999998</v>
+        <v>1.5677</v>
       </c>
       <c r="L2" t="n">
-        <v>23.3996</v>
+        <v>8.352699999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2424</v>
+        <v>-6.005599999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>1.2735</v>
+        <v>-4.335900000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9692</v>
+        <v>-1.6697</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8964</v>
+        <v>1.836</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.9948</v>
+        <v>-5.7375</v>
       </c>
       <c r="R2" t="n">
-        <v>11.8915</v>
+        <v>7.5735</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3782</v>
+        <v>-0.7133</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7336</v>
+        <v>1.1084</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6447</v>
+        <v>-1.8217</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.0803</v>
+        <v>1.8365</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.1892</v>
+        <v>3.0693</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.8911</v>
+        <v>-1.2329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>20.8653</v>
+        <v>5.9405</v>
       </c>
       <c r="E3" t="n">
-        <v>17.2959</v>
+        <v>3.9698</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5693</v>
+        <v>1.9707</v>
       </c>
       <c r="G3" t="n">
-        <v>5.760999999999999</v>
+        <v>0.4828000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.1274</v>
+        <v>-4.5128</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8884</v>
+        <v>4.995699999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>14.936</v>
+        <v>-0.01580000000000004</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.142499999999999</v>
+        <v>-3.6839</v>
       </c>
       <c r="L3" t="n">
-        <v>20.0786</v>
+        <v>3.6681</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.174700000000001</v>
+        <v>0.4987999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.9845</v>
+        <v>-0.8287</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.1902</v>
+        <v>1.3277</v>
       </c>
       <c r="P3" t="n">
-        <v>8.393799999999999</v>
+        <v>0.918</v>
       </c>
       <c r="Q3" t="n">
-        <v>-13.5235</v>
+        <v>-3.4425</v>
       </c>
       <c r="R3" t="n">
-        <v>21.9179</v>
+        <v>4.3605</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2585</v>
+        <v>6.225</v>
       </c>
       <c r="T3" t="n">
-        <v>3.9747</v>
+        <v>5.2641</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.2332</v>
+        <v>0.9609999999999997</v>
       </c>
       <c r="V3" t="n">
-        <v>6.9684</v>
+        <v>-1.6855</v>
       </c>
       <c r="W3" t="n">
-        <v>11.909</v>
+        <v>2.164</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.9403</v>
+        <v>-3.849600000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>14.9883</v>
+        <v>5.7254</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3898</v>
+        <v>2.916</v>
       </c>
       <c r="F4" t="n">
-        <v>8.5982</v>
+        <v>2.8095</v>
       </c>
       <c r="G4" t="n">
-        <v>10.8076</v>
+        <v>6.2989</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0172</v>
+        <v>0.2429000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>7.790100000000001</v>
+        <v>6.055899999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9.648199999999999</v>
+        <v>5.873699999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>7.5387</v>
+        <v>0.3369000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1095</v>
+        <v>5.5368</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1593</v>
+        <v>0.4252000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.5213</v>
+        <v>-0.09390000000000004</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6806</v>
+        <v>0.5191</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5649</v>
+        <v>0.9179999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-22.8507</v>
+        <v>-2.295</v>
       </c>
       <c r="R4" t="n">
-        <v>20.2855</v>
+        <v>3.213</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.888699999999999</v>
+        <v>0.1316000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9740000000000002</v>
+        <v>-0.2725</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.8627</v>
+        <v>0.4042</v>
       </c>
       <c r="V4" t="n">
-        <v>11.6341</v>
+        <v>-1.623</v>
       </c>
       <c r="W4" t="n">
-        <v>18.6181</v>
+        <v>-0.3901</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.9837</v>
+        <v>-1.2329</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>13.9367</v>
+        <v>3.6033</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.2925</v>
+        <v>2.8121</v>
       </c>
       <c r="F5" t="n">
-        <v>23.2292</v>
+        <v>0.7912000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>8.466699999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="H5" t="n">
-        <v>2.746</v>
+        <v>3.3329</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7207</v>
+        <v>-2.3346</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5921</v>
+        <v>2.6637</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4034</v>
+        <v>6.0903</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.8116</v>
+        <v>-3.4264</v>
       </c>
       <c r="M5" t="n">
-        <v>5.874899999999999</v>
+        <v>-1.6652</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6577</v>
+        <v>-2.7573</v>
       </c>
       <c r="O5" t="n">
-        <v>7.5323</v>
+        <v>1.0921</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4977</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q5" t="n">
-        <v>-17.4874</v>
+        <v>-8.032499999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>20.9851</v>
+        <v>6.8849</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1488</v>
+        <v>-0.8776</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3004</v>
+        <v>1.1735</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.1516</v>
+        <v>-2.0511</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8234999999999999</v>
+        <v>4.6298</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3027</v>
+        <v>7.0072</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4792</v>
+        <v>-2.3774</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>13.8992</v>
+        <v>0.3884999999999996</v>
       </c>
       <c r="E6" t="n">
-        <v>7.520300000000002</v>
+        <v>-4.1497</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3785</v>
+        <v>4.5382</v>
       </c>
       <c r="G6" t="n">
-        <v>1.082500000000001</v>
+        <v>2.1358</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.7443</v>
+        <v>-0.9594</v>
       </c>
       <c r="I6" t="n">
-        <v>11.8268</v>
+        <v>3.0951</v>
       </c>
       <c r="J6" t="n">
-        <v>2.965</v>
+        <v>1.8899</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.5284</v>
+        <v>1.3215</v>
       </c>
       <c r="L6" t="n">
-        <v>10.4934</v>
+        <v>0.5682000000000003</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8822</v>
+        <v>0.2459000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.2158</v>
+        <v>-2.2811</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3334</v>
+        <v>2.5269</v>
       </c>
       <c r="P6" t="n">
-        <v>11.8915</v>
+        <v>-3.213</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.197</v>
+        <v>-9.1799</v>
       </c>
       <c r="R6" t="n">
-        <v>16.0882</v>
+        <v>5.9669</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7975</v>
+        <v>1.9441</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3361000000000001</v>
+        <v>2.235</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1337</v>
+        <v>-0.2908000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.723</v>
+        <v>-0.4785999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>8.4171</v>
+        <v>0.9052000000000002</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.6938</v>
+        <v>-1.3838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. MORIN</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5872</v>
+        <v>0.3651</v>
       </c>
       <c r="E7" t="n">
-        <v>4.307</v>
+        <v>1.790499999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7201000000000002</v>
+        <v>-1.4251</v>
       </c>
       <c r="G7" t="n">
-        <v>6.839600000000001</v>
+        <v>-1.4797</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0669</v>
+        <v>-2.905</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7723</v>
+        <v>1.4253</v>
       </c>
       <c r="J7" t="n">
-        <v>2.364099999999999</v>
+        <v>2.4847</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6713</v>
+        <v>0.06980000000000031</v>
       </c>
       <c r="L7" t="n">
-        <v>4.0351</v>
+        <v>2.4149</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4754</v>
+        <v>-3.9644</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7382</v>
+        <v>-2.9748</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7372</v>
+        <v>-0.9896000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>6.7618</v>
+        <v>4.3605</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0313</v>
+        <v>-1.1475</v>
       </c>
       <c r="R7" t="n">
-        <v>9.793100000000001</v>
+        <v>5.508</v>
       </c>
       <c r="S7" t="n">
-        <v>0.004000000000000059</v>
+        <v>-1.5843</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9488</v>
+        <v>-0.7798</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9447999999999999</v>
+        <v>-0.8046000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-10.0176</v>
+        <v>-0.9312</v>
       </c>
       <c r="W7" t="n">
-        <v>4.0257</v>
+        <v>1.2329</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.0433</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>Y. MORIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4322</v>
+        <v>-3.2228</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.869800000000001</v>
+        <v>-2.0531</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4367</v>
+        <v>-1.1697</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7014</v>
+        <v>-2.771</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1461</v>
+        <v>-3.9535</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4446999999999999</v>
+        <v>1.1826</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4047999999999998</v>
+        <v>-3.6319</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2441</v>
+        <v>-3.9653</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6486000000000001</v>
+        <v>0.3335</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1065</v>
+        <v>0.8609</v>
       </c>
       <c r="N8" t="n">
-        <v>1.9026</v>
+        <v>0.01190000000000002</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2042</v>
+        <v>0.8492</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.5649</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.9948</v>
+        <v>-2.295</v>
       </c>
       <c r="R8" t="n">
-        <v>4.4302</v>
+        <v>2.295</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.3985</v>
+        <v>0.7811999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6714</v>
+        <v>1.257</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.727</v>
+        <v>-0.4758</v>
       </c>
       <c r="V8" t="n">
-        <v>1.829199999999999</v>
+        <v>-1.2329</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2019</v>
+        <v>2.6167</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3727</v>
+        <v>-3.8496</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1343</v>
+        <v>-3.2758</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3757</v>
+        <v>-2.2732</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2413999999999996</v>
+        <v>-1.0026</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.428199999999999</v>
+        <v>-0.1823000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-12.6518</v>
+        <v>-0.01060000000000003</v>
       </c>
       <c r="I9" t="n">
-        <v>7.223599999999999</v>
+        <v>-0.1716</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6133</v>
+        <v>0.06490000000000007</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.9292</v>
+        <v>0.0954</v>
       </c>
       <c r="L9" t="n">
-        <v>5.5425</v>
+        <v>-0.03029999999999988</v>
       </c>
       <c r="M9" t="n">
-        <v>-8.041</v>
+        <v>-0.2471</v>
       </c>
       <c r="N9" t="n">
-        <v>-9.722300000000001</v>
+        <v>-0.1057</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6811</v>
+        <v>-0.1414</v>
       </c>
       <c r="P9" t="n">
-        <v>6.5286</v>
+        <v>-0.9179999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-11.658</v>
+        <v>-2.295</v>
       </c>
       <c r="R9" t="n">
-        <v>18.1869</v>
+        <v>1.377</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7518</v>
+        <v>-0.8801</v>
       </c>
       <c r="T9" t="n">
-        <v>4.9804</v>
+        <v>-0.043</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2285</v>
+        <v>-0.8371</v>
       </c>
       <c r="V9" t="n">
-        <v>-9.986800000000001</v>
+        <v>-1.2954</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.3111</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.675699999999999</v>
+        <v>-1.2954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.067499999999999</v>
+        <v>-4.1103</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.760600000000001</v>
+        <v>-5.6653</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.3066</v>
+        <v>1.5551</v>
       </c>
       <c r="G10" t="n">
-        <v>-10.6156</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-16.8692</v>
+        <v>-0.542</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2536</v>
+        <v>0.2895</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.6922</v>
+        <v>0.5153999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-15.0015</v>
+        <v>0.334</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3096</v>
+        <v>0.1815999999999998</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9231</v>
+        <v>-0.7679</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8674</v>
+        <v>-0.876</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.05630000000000006</v>
+        <v>0.1081</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6996</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.6583</v>
+        <v>-4.59</v>
       </c>
       <c r="R10" t="n">
-        <v>12.3576</v>
+        <v>4.59</v>
       </c>
       <c r="S10" t="n">
-        <v>15.5498</v>
+        <v>-1.6939</v>
       </c>
       <c r="T10" t="n">
-        <v>15.455</v>
+        <v>-1.5908</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09509999999999974</v>
+        <v>-0.103</v>
       </c>
       <c r="V10" t="n">
-        <v>-12.7017</v>
+        <v>-2.164</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1347</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.8363</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.6572</v>
+        <v>-6.5344</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.9209</v>
+        <v>-2.7535</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2635</v>
+        <v>-3.780899999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.2888</v>
+        <v>-5.2017</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7784999999999999</v>
+        <v>-6.0977</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.067600000000001</v>
+        <v>0.8959999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.9499</v>
+        <v>0.1154999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3440000000000001</v>
+        <v>-0.9885000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.2939</v>
+        <v>1.104</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3383</v>
+        <v>-5.3172</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4345000000000001</v>
+        <v>-5.1091</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.773</v>
+        <v>-0.2081</v>
       </c>
       <c r="P11" t="n">
-        <v>3.497199999999999</v>
+        <v>2.754</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.995100000000001</v>
+        <v>-4.59</v>
       </c>
       <c r="R11" t="n">
-        <v>10.4923</v>
+        <v>7.344</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.0629</v>
+        <v>-0.6898</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9756</v>
+        <v>0.639</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.0876</v>
+        <v>-1.3288</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.802999999999999</v>
+        <v>-3.3969</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.082</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.802999999999999</v>
+        <v>-4.4789</v>
       </c>
     </row>
     <row r="12">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.8919</v>
+        <v>-8.9101</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.3301</v>
+        <v>-7.0583</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.561999999999999</v>
+        <v>-1.8518</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.4778</v>
+        <v>-8.366999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.6518</v>
+        <v>-3.6988</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.825699999999999</v>
+        <v>-4.668200000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.1368</v>
+        <v>-3.1529</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8951</v>
+        <v>-1.253</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.2417</v>
+        <v>-1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.341000000000001</v>
+        <v>-5.2139</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.7573</v>
+        <v>-2.4457</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.584</v>
+        <v>-2.7682</v>
       </c>
       <c r="P12" t="n">
-        <v>6.762</v>
+        <v>2.5245</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.6944</v>
+        <v>-3.4425</v>
       </c>
       <c r="R12" t="n">
-        <v>14.4564</v>
+        <v>5.967000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6842</v>
+        <v>-1.8347</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0898</v>
+        <v>-0.4629</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.7737</v>
+        <v>-1.3718</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.4919</v>
+        <v>-1.2329</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4119</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.9038</v>
+        <v>-1.2329</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>58.74319999999999</v>
+        <v>-3.156900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>4.725500000000013</v>
+        <v>-4.104199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>54.0155</v>
+        <v>0.9478999999999993</v>
       </c>
       <c r="G13" t="n">
-        <v>23.30329999999999</v>
+        <v>-4.423599999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-47.2036</v>
+        <v>-21.8721</v>
       </c>
       <c r="I13" t="n">
-        <v>70.50620000000001</v>
+        <v>17.4487</v>
       </c>
       <c r="J13" t="n">
-        <v>38.1476</v>
+        <v>16.7274</v>
       </c>
       <c r="K13" t="n">
-        <v>-21.8248</v>
+        <v>-0.0750999999999995</v>
       </c>
       <c r="L13" t="n">
-        <v>59.9725</v>
+        <v>16.8031</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.8418</v>
+        <v>-21.1505</v>
       </c>
       <c r="N13" t="n">
-        <v>-25.3775</v>
+        <v>-21.7963</v>
       </c>
       <c r="O13" t="n">
-        <v>10.5345</v>
+        <v>0.6460999999999997</v>
       </c>
       <c r="P13" t="n">
-        <v>47.7988</v>
+        <v>8.032499999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-113.0853</v>
+        <v>-47.0474</v>
       </c>
       <c r="R13" t="n">
-        <v>160.8847</v>
+        <v>55.0798</v>
       </c>
       <c r="S13" t="n">
-        <v>8.7423</v>
+        <v>0.8081999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>31.1458</v>
+        <v>8.528</v>
       </c>
       <c r="U13" t="n">
-        <v>-22.403</v>
+        <v>-7.7195</v>
       </c>
       <c r="V13" t="n">
-        <v>-21.1031</v>
+        <v>-7.5741</v>
       </c>
       <c r="W13" t="n">
-        <v>48.5208</v>
+        <v>17.6872</v>
       </c>
       <c r="X13" t="n">
-        <v>-69.6229</v>
+        <v>-25.2614</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6.873699999999999</v>
+        <v>8.1393</v>
       </c>
       <c r="E2" t="n">
-        <v>8.360500000000002</v>
+        <v>3.6221</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.486699999999999</v>
+        <v>4.516999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9147</v>
+        <v>9.058</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.7681</v>
+        <v>-1.533</v>
       </c>
       <c r="I2" t="n">
-        <v>6.682999999999999</v>
+        <v>10.5909</v>
       </c>
       <c r="J2" t="n">
-        <v>9.920199999999999</v>
+        <v>8.856300000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5677</v>
+        <v>-1.1829</v>
       </c>
       <c r="L2" t="n">
-        <v>8.352699999999999</v>
+        <v>10.039</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.005599999999999</v>
+        <v>0.2017000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.335900000000001</v>
+        <v>-0.3501000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6697</v>
+        <v>0.5519000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.836</v>
+        <v>0.7018</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.7375</v>
+        <v>-4.9135</v>
       </c>
       <c r="R2" t="n">
-        <v>7.5735</v>
+        <v>5.6153</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7133</v>
+        <v>-0.82</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1084</v>
+        <v>-0.9871</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.8217</v>
+        <v>0.1670999999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8365</v>
+        <v>-0.8007000000000002</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0693</v>
+        <v>0.6663000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2329</v>
+        <v>-1.467</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9405</v>
+        <v>4.7756</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9698</v>
+        <v>4.654999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9707</v>
+        <v>0.1207999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4828000000000001</v>
+        <v>-0.5749</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.5128</v>
+        <v>0.3614999999999995</v>
       </c>
       <c r="I3" t="n">
-        <v>4.995699999999999</v>
+        <v>-0.9358000000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.01580000000000004</v>
+        <v>4.216500000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.6839</v>
+        <v>6.244199999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6681</v>
+        <v>-2.0278</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4987999999999999</v>
+        <v>-4.7913</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8287</v>
+        <v>-5.8829</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3277</v>
+        <v>1.0914</v>
       </c>
       <c r="P3" t="n">
-        <v>0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4425</v>
+        <v>-10.5288</v>
       </c>
       <c r="R3" t="n">
-        <v>4.3605</v>
+        <v>9.5928</v>
       </c>
       <c r="S3" t="n">
-        <v>6.225</v>
+        <v>-0.5012999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>5.2641</v>
+        <v>1.3797</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9609999999999997</v>
+        <v>-1.881</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6855</v>
+        <v>6.7875</v>
       </c>
       <c r="W3" t="n">
-        <v>2.164</v>
+        <v>9.587399999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.849600000000001</v>
+        <v>-2.7999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7254</v>
+        <v>3.5804</v>
       </c>
       <c r="E4" t="n">
-        <v>2.916</v>
+        <v>5.909800000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8095</v>
+        <v>-2.329400000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2989</v>
+        <v>-0.2527999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2429000000000001</v>
+        <v>-2.6825</v>
       </c>
       <c r="I4" t="n">
-        <v>6.055899999999999</v>
+        <v>2.4298</v>
       </c>
       <c r="J4" t="n">
-        <v>5.873699999999999</v>
+        <v>6.2227</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3369000000000001</v>
+        <v>2.1279</v>
       </c>
       <c r="L4" t="n">
-        <v>5.5368</v>
+        <v>4.0946</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4252000000000001</v>
+        <v>-6.4751</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.09390000000000004</v>
+        <v>-4.8105</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5191</v>
+        <v>-1.665</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9179999999999999</v>
+        <v>6.5512</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.295</v>
+        <v>-1.4039</v>
       </c>
       <c r="R4" t="n">
-        <v>3.213</v>
+        <v>7.9551</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1316000000000002</v>
+        <v>-0.7244999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2725</v>
+        <v>-0.1074000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4042</v>
+        <v>-0.6169</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.623</v>
+        <v>-1.9938</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3901</v>
+        <v>1.1985</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2329</v>
+        <v>-3.1923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6033</v>
+        <v>2.6328</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8121</v>
+        <v>2.4541</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7912000000000001</v>
+        <v>0.1784999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9984</v>
+        <v>-2.664899999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3329</v>
+        <v>-8.0747</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3346</v>
+        <v>5.4098</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6637</v>
+        <v>-0.8076000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>6.0903</v>
+        <v>-6.0417</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.4264</v>
+        <v>5.2343</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6652</v>
+        <v>-1.8571</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.7573</v>
+        <v>-2.0328</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0921</v>
+        <v>0.1757</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1475</v>
+        <v>0.2341</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.032499999999999</v>
+        <v>-6.083399999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>6.8849</v>
+        <v>6.317299999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8776</v>
+        <v>5.734900000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1735</v>
+        <v>5.0887</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.0511</v>
+        <v>0.6463999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>4.6298</v>
+        <v>-0.6714999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>7.0072</v>
+        <v>4.2564</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3774</v>
+        <v>-4.927899999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3884999999999996</v>
+        <v>1.509500000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.1497</v>
+        <v>8.167</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5382</v>
+        <v>-6.6575</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1358</v>
+        <v>-0.1238000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9594</v>
+        <v>-7.1924</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0951</v>
+        <v>7.068600000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8899</v>
+        <v>12.1401</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3215</v>
+        <v>0.5659000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5682000000000003</v>
+        <v>11.5738</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2459000000000002</v>
+        <v>-12.2639</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2811</v>
+        <v>-7.758599999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5269</v>
+        <v>-4.505100000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.213</v>
+        <v>0.9359</v>
       </c>
       <c r="Q6" t="n">
-        <v>-9.1799</v>
+        <v>-9.8269</v>
       </c>
       <c r="R6" t="n">
-        <v>5.9669</v>
+        <v>10.7627</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9441</v>
+        <v>-2.371</v>
       </c>
       <c r="T6" t="n">
-        <v>2.235</v>
+        <v>0.3887000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2908000000000001</v>
+        <v>-2.7599</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4785999999999999</v>
+        <v>3.0682</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9052000000000002</v>
+        <v>5.4651</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3838</v>
+        <v>-2.3969</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3651</v>
+        <v>0.3484</v>
       </c>
       <c r="E7" t="n">
-        <v>1.790499999999999</v>
+        <v>-0.2208</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4251</v>
+        <v>0.5692</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4797</v>
+        <v>-0.2638</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.905</v>
+        <v>-0.2145</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4253</v>
+        <v>-0.0493</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4847</v>
+        <v>-0.1734</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06980000000000031</v>
+        <v>-0.21</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4149</v>
+        <v>0.0366</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.9644</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.9748</v>
+        <v>-0.0045</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9896000000000001</v>
+        <v>-0.0859</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3605</v>
+        <v>0.9359</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1475</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5.508</v>
+        <v>0.9359</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5843</v>
+        <v>-0.1894</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7798</v>
+        <v>-0.0474</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8046000000000001</v>
+        <v>-0.142</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9312</v>
+        <v>-0.1343</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2329</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.164</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. MORIN</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2228</v>
+        <v>-0.7211999999999996</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0531</v>
+        <v>-2.1486</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1697</v>
+        <v>1.4272</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.771</v>
+        <v>-0.008799999999999975</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9535</v>
+        <v>0.4303999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1826</v>
+        <v>-0.4391999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.6319</v>
+        <v>0.04959999999999998</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.9653</v>
+        <v>0.3495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3335</v>
+        <v>-0.2999999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8609</v>
+        <v>-0.05840000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01190000000000002</v>
+        <v>0.08079999999999998</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8492</v>
+        <v>-0.1392</v>
       </c>
       <c r="P8" t="n">
+        <v>0.9359</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-2.3398</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.2757</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.3104999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.4520999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-1.338</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-2.295</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.7811999999999999</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.257</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.4758</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.2329</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.6167</v>
-      </c>
       <c r="X8" t="n">
-        <v>-3.8496</v>
+        <v>-1.338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2758</v>
+        <v>-2.2648</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2732</v>
+        <v>-7.0969</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0026</v>
+        <v>4.8319</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1823000000000001</v>
+        <v>4.8602</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.01060000000000003</v>
+        <v>-2.8278</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1716</v>
+        <v>7.6882</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06490000000000007</v>
+        <v>5.027699999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0954</v>
+        <v>1.5967</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.03029999999999988</v>
+        <v>3.4311</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2471</v>
+        <v>-0.1675999999999996</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1057</v>
+        <v>-4.4245</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1414</v>
+        <v>4.257</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9179999999999999</v>
+        <v>-7.253</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.295</v>
+        <v>-16.6121</v>
       </c>
       <c r="R9" t="n">
-        <v>1.377</v>
+        <v>9.3589</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8801</v>
+        <v>1.8535</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.043</v>
+        <v>2.6176</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8371</v>
+        <v>-0.7641</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2954</v>
+        <v>-1.7253</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8699</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2954</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>Y. MORIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1103</v>
+        <v>-2.5888</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6653</v>
+        <v>-4.0081</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5551</v>
+        <v>1.4193</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2524999999999999</v>
+        <v>-1.5275</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.542</v>
+        <v>-4.305000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2895</v>
+        <v>2.7773</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5153999999999999</v>
+        <v>-2.1269</v>
       </c>
       <c r="K10" t="n">
-        <v>0.334</v>
+        <v>-3.8471</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1815999999999998</v>
+        <v>1.7203</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7679</v>
+        <v>0.5992000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.876</v>
+        <v>-0.4579</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1081</v>
+        <v>1.057</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.4037</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.59</v>
+        <v>-6.0832</v>
       </c>
       <c r="R10" t="n">
-        <v>4.59</v>
+        <v>4.6795</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6939</v>
+        <v>1.4067</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5908</v>
+        <v>1.5366</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.103</v>
+        <v>-0.1301</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.164</v>
+        <v>-1.0642</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.6654</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.164</v>
+        <v>-3.7296</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5344</v>
+        <v>-4.371799999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7535</v>
+        <v>-7.2544</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.780899999999999</v>
+        <v>2.8827</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.2017</v>
+        <v>-1.6113</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.0977</v>
+        <v>-0.2092000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8959999999999999</v>
+        <v>-1.4023</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1154999999999999</v>
+        <v>1.1817</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9885000000000002</v>
+        <v>1.2403</v>
       </c>
       <c r="L11" t="n">
-        <v>1.104</v>
+        <v>-0.05860000000000021</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.3172</v>
+        <v>-2.793</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.1091</v>
+        <v>-1.4495</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2081</v>
+        <v>-1.3437</v>
       </c>
       <c r="P11" t="n">
-        <v>2.754</v>
+        <v>1.4038</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.59</v>
+        <v>-6.0832</v>
       </c>
       <c r="R11" t="n">
-        <v>7.344</v>
+        <v>7.487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6898</v>
+        <v>-2.6974</v>
       </c>
       <c r="T11" t="n">
-        <v>0.639</v>
+        <v>-2.353</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3288</v>
+        <v>-0.3443999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.3969</v>
+        <v>-1.4671</v>
       </c>
       <c r="W11" t="n">
-        <v>1.082</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.4789</v>
+        <v>-1.4671</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,148 +1342,226 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.9101</v>
+        <v>-11.8816</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0583</v>
+        <v>-2.353000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8518</v>
+        <v>-9.528700000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.366999999999999</v>
+        <v>-7.7082</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.6988</v>
+        <v>-11.3217</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.668200000000001</v>
+        <v>3.6135</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.1529</v>
+        <v>2.839399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.253</v>
+        <v>-2.136200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9</v>
+        <v>4.975700000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.2139</v>
+        <v>-10.5476</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4457</v>
+        <v>-9.1854</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.7682</v>
+        <v>-1.3622</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5245</v>
+        <v>1.8717</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4425</v>
+        <v>-8.4232</v>
       </c>
       <c r="R12" t="n">
-        <v>5.967000000000001</v>
+        <v>10.2947</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8347</v>
+        <v>-2.4499</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4629</v>
+        <v>0.03820000000000012</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3718</v>
+        <v>-2.488</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2329</v>
+        <v>-3.5952</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.1923</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2329</v>
+        <v>-6.787500000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Y. KRAAG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Joventut Badalona</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-14.7737</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-9.3583</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-5.4155</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-12.8332</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-4.5658</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-8.267199999999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-4.5651</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.5900999999999997</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-3.975</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-8.2681</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-3.9757</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-4.2924</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.0418</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-4.9135</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.955</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-2.7197</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.9442</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.7758</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-2.2625</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.0641</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-3.3266</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Joventut Badalona</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-3.156900000000002</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-4.104199999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9478999999999993</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-4.423599999999998</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-21.8721</v>
-      </c>
-      <c r="I13" t="n">
-        <v>17.4487</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16.7274</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.0750999999999995</v>
-      </c>
-      <c r="L13" t="n">
-        <v>16.8031</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-21.1505</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-21.7963</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.6460999999999997</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8.032499999999999</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-47.0474</v>
-      </c>
-      <c r="R13" t="n">
-        <v>55.0798</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.8081999999999998</v>
-      </c>
-      <c r="T13" t="n">
-        <v>8.528</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-7.7195</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-7.5741</v>
-      </c>
-      <c r="W13" t="n">
-        <v>17.6872</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-25.2614</v>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-15.6159</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-7.6321</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-7.984500000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-13.651</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-42.1347</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28.4843</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32.86099999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.8835</v>
+      </c>
+      <c r="L14" t="n">
+        <v>34.74400000000001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-46.5116</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-40.2516</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-6.2605</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7.019499999999999</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-77.21149999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>84.2299</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-3.7886</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6.752199999999998</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-10.5408</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-5.1969</v>
+      </c>
+      <c r="W14" t="n">
+        <v>29.9654</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-35.1623</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1393</v>
+        <v>12.1752</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6221</v>
+        <v>5.611400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.516999999999999</v>
+        <v>6.5637</v>
       </c>
       <c r="G2" t="n">
-        <v>9.058</v>
+        <v>11.9554</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.533</v>
+        <v>-1.0532</v>
       </c>
       <c r="I2" t="n">
-        <v>10.5909</v>
+        <v>13.0085</v>
       </c>
       <c r="J2" t="n">
-        <v>8.856300000000001</v>
+        <v>11.1984</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1829</v>
+        <v>-0.8809</v>
       </c>
       <c r="L2" t="n">
-        <v>10.039</v>
+        <v>12.0793</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2017000000000001</v>
+        <v>0.7570999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3501000000000001</v>
+        <v>-0.1722</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5519000000000001</v>
+        <v>0.9293</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7018</v>
+        <v>-9.999999999987796e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.9135</v>
+        <v>-6.266</v>
       </c>
       <c r="R2" t="n">
-        <v>5.6153</v>
+        <v>6.2659</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.82</v>
+        <v>0.1077999999999998</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9871</v>
+        <v>0.001600000000000018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1670999999999998</v>
+        <v>0.106</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8007000000000002</v>
+        <v>0.1118999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6663000000000001</v>
+        <v>0.6772</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.467</v>
+        <v>-0.5653</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7756</v>
+        <v>7.265400000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4.654999999999999</v>
+        <v>6.161300000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1207999999999999</v>
+        <v>1.1042</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5749</v>
+        <v>1.5377</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3614999999999995</v>
+        <v>-1.5645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9358000000000002</v>
+        <v>3.1025</v>
       </c>
       <c r="J3" t="n">
-        <v>4.216500000000001</v>
+        <v>4.3462</v>
       </c>
       <c r="K3" t="n">
-        <v>6.244199999999999</v>
+        <v>0.9818999999999998</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.0278</v>
+        <v>3.3642</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.7913</v>
+        <v>-2.8082</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.8829</v>
+        <v>-2.5464</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0914</v>
+        <v>-0.2617999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9359</v>
+        <v>6.7301</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.5288</v>
+        <v>-1.6246</v>
       </c>
       <c r="R3" t="n">
-        <v>9.5928</v>
+        <v>8.354700000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5012999999999999</v>
+        <v>0.2105000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3797</v>
+        <v>0.6191000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.881</v>
+        <v>-0.4084</v>
       </c>
       <c r="V3" t="n">
-        <v>6.7875</v>
+        <v>-1.213</v>
       </c>
       <c r="W3" t="n">
-        <v>9.587399999999999</v>
+        <v>2.8206</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7999</v>
+        <v>-4.0336</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5804</v>
+        <v>4.0988</v>
       </c>
       <c r="E4" t="n">
-        <v>5.909800000000001</v>
+        <v>1.6126</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.329400000000001</v>
+        <v>2.4861</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2527999999999999</v>
+        <v>0.3716999999999997</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6825</v>
+        <v>0.9353000000000002</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4298</v>
+        <v>-0.5634999999999994</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2227</v>
+        <v>3.3605</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1279</v>
+        <v>4.559100000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0946</v>
+        <v>-1.1986</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.4751</v>
+        <v>-2.9888</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.8105</v>
+        <v>-3.6238</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.665</v>
+        <v>0.6351</v>
       </c>
       <c r="P4" t="n">
-        <v>6.5512</v>
+        <v>-2.7848</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4039</v>
+        <v>-13.4602</v>
       </c>
       <c r="R4" t="n">
-        <v>7.9551</v>
+        <v>10.6753</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7244999999999999</v>
+        <v>-2.5198</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1074000000000001</v>
+        <v>-0.1355000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6169</v>
+        <v>-2.3843</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.9938</v>
+        <v>9.031700000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1985</v>
+        <v>11.8479</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.1923</v>
+        <v>-2.816</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>D. NIEBLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6328</v>
+        <v>0.5206</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4541</v>
+        <v>0.5206</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1784999999999999</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.664899999999999</v>
+        <v>0.5206</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.0747</v>
+        <v>0.5206</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4098</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8076000000000001</v>
+        <v>0.5206</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.0417</v>
+        <v>0.5206</v>
       </c>
       <c r="L5" t="n">
-        <v>5.2343</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8571</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0328</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1757</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2341</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.083399999999999</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6.317299999999999</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5.734900000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>5.0887</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6463999999999999</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6714999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>4.2564</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.927899999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.509500000000001</v>
+        <v>0.3397</v>
       </c>
       <c r="E6" t="n">
-        <v>8.167</v>
+        <v>-0.2053</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.6575</v>
+        <v>0.545</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1238000000000001</v>
+        <v>-0.2625</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.1924</v>
+        <v>-0.2165</v>
       </c>
       <c r="I6" t="n">
-        <v>7.068600000000001</v>
+        <v>-0.046</v>
       </c>
       <c r="J6" t="n">
-        <v>12.1401</v>
+        <v>-0.175</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5659000000000001</v>
+        <v>-0.2118</v>
       </c>
       <c r="L6" t="n">
-        <v>11.5738</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.2639</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.758599999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.505100000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q6" t="n">
-        <v>-9.8269</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7627</v>
+        <v>0.9283</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.371</v>
+        <v>-0.1848</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3887000000000001</v>
+        <v>-0.0303</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.7599</v>
+        <v>-0.1546</v>
       </c>
       <c r="V6" t="n">
-        <v>3.0682</v>
+        <v>-0.1413</v>
       </c>
       <c r="W6" t="n">
-        <v>5.4651</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3969</v>
+        <v>-0.1413</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>Y. MORIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3484</v>
+        <v>-0.08910000000000018</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2208</v>
+        <v>0.06210000000000027</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5692</v>
+        <v>-0.1514</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2638</v>
+        <v>4.9427</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2145</v>
+        <v>1.4104</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0493</v>
+        <v>3.5323</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1734</v>
+        <v>3.4424</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.21</v>
+        <v>0.7198</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0366</v>
+        <v>2.7228</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09039999999999999</v>
+        <v>1.5004</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0045</v>
+        <v>0.6908</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0859</v>
+        <v>0.8096000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9359</v>
+        <v>1.3925</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.1773</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9359</v>
+        <v>5.569800000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1894</v>
+        <v>-0.2768</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0474</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.142</v>
+        <v>-0.3669999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1343</v>
+        <v>-6.1477</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.7066000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1343</v>
+        <v>-6.854200000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7211999999999996</v>
+        <v>-0.1298999999999997</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1486</v>
+        <v>2.9776</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4272</v>
+        <v>-3.1073</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008799999999999975</v>
+        <v>2.2306</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4303999999999999</v>
+        <v>-4.1715</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4391999999999999</v>
+        <v>6.4021</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04959999999999998</v>
+        <v>10.7875</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3495</v>
+        <v>0.5159000000000002</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2999999999999999</v>
+        <v>10.2717</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05840000000000001</v>
+        <v>-8.556900000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08079999999999998</v>
+        <v>-4.6873</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1392</v>
+        <v>-3.8696</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9359</v>
+        <v>-3.481</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3398</v>
+        <v>-15.0847</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2757</v>
+        <v>11.6036</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3104999999999999</v>
+        <v>-3.0885</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1418</v>
+        <v>0.1378999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4520999999999999</v>
+        <v>-3.2264</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.338</v>
+        <v>4.2091</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>7.136800000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.338</v>
+        <v>-2.9278</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2648</v>
+        <v>-1.5065</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.0969</v>
+        <v>-3.0991</v>
       </c>
       <c r="F9" t="n">
-        <v>4.8319</v>
+        <v>1.5924</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8602</v>
+        <v>-1.1064</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8278</v>
+        <v>0.2090000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>7.6882</v>
+        <v>-1.3153</v>
       </c>
       <c r="J9" t="n">
-        <v>5.027699999999999</v>
+        <v>-1.793</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5967</v>
+        <v>-0.3602</v>
       </c>
       <c r="L9" t="n">
-        <v>3.4311</v>
+        <v>-1.4328</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1675999999999996</v>
+        <v>0.6866000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.4245</v>
+        <v>0.5694</v>
       </c>
       <c r="O9" t="n">
-        <v>4.257</v>
+        <v>0.1173</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.253</v>
+        <v>1.3924</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16.6121</v>
+        <v>-2.3208</v>
       </c>
       <c r="R9" t="n">
-        <v>9.3589</v>
+        <v>3.7132</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8535</v>
+        <v>-0.6914</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6176</v>
+        <v>-0.05689999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7641</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7253</v>
+        <v>-1.1012</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8699</v>
+        <v>1.0717</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.5952</v>
+        <v>-2.1729</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. MORIN</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5888</v>
+        <v>-3.1267</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0081</v>
+        <v>-10.3322</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4193</v>
+        <v>7.2055</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5275</v>
+        <v>3.7852</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.305000000000001</v>
+        <v>0.2922999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7773</v>
+        <v>3.493</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1269</v>
+        <v>2.2667</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.8471</v>
+        <v>2.7592</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7203</v>
+        <v>-0.4926000000000004</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5992000000000001</v>
+        <v>1.5185</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4579</v>
+        <v>-2.467</v>
       </c>
       <c r="O10" t="n">
-        <v>1.057</v>
+        <v>3.9856</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4037</v>
+        <v>-4.4093</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.0832</v>
+        <v>-15.3168</v>
       </c>
       <c r="R10" t="n">
-        <v>4.6795</v>
+        <v>10.9075</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4067</v>
+        <v>-0.5008</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5366</v>
+        <v>1.2221</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1301</v>
+        <v>-1.7228</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0642</v>
+        <v>-2.002</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6654</v>
+        <v>1.4957</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.7296</v>
+        <v>-3.4977</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.371799999999999</v>
+        <v>-4.6901</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.2544</v>
+        <v>-0.9852999999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8827</v>
+        <v>-3.705</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6113</v>
+        <v>-4.792199999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2092000000000001</v>
+        <v>-6.641299999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4023</v>
+        <v>1.8492</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1817</v>
+        <v>-1.3128</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2403</v>
+        <v>-4.7712</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.05860000000000021</v>
+        <v>3.4585</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.793</v>
+        <v>-3.4794</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4495</v>
+        <v>-1.8702</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3437</v>
+        <v>-1.6094</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4038</v>
+        <v>-0.4641000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.0832</v>
+        <v>-7.4263</v>
       </c>
       <c r="R11" t="n">
-        <v>7.487</v>
+        <v>6.962200000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6974</v>
+        <v>4.3126</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.353</v>
+        <v>5.4691</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3443999999999999</v>
+        <v>-1.1565</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4671</v>
+        <v>-3.7462</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.2847</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4671</v>
+        <v>-6.030900000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.8816</v>
+        <v>-5.8216</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.353000000000001</v>
+        <v>-0.7347000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.528700000000001</v>
+        <v>-5.0867</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.7082</v>
+        <v>-0.9582999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.3217</v>
+        <v>-3.467300000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6135</v>
+        <v>2.509</v>
       </c>
       <c r="J12" t="n">
-        <v>2.839399999999999</v>
+        <v>5.7563</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.136200000000001</v>
+        <v>2.6524</v>
       </c>
       <c r="L12" t="n">
-        <v>4.975700000000001</v>
+        <v>3.104</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.5476</v>
+        <v>-6.7146</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.1854</v>
+        <v>-6.119599999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3622</v>
+        <v>-0.5952000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8717</v>
+        <v>0.6960999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.4232</v>
+        <v>-8.818900000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2947</v>
+        <v>9.514900000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4499</v>
+        <v>-1.56</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03820000000000012</v>
+        <v>0.4374</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.488</v>
+        <v>-1.9973</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.5952</v>
+        <v>-3.9995</v>
       </c>
       <c r="W12" t="n">
-        <v>3.1923</v>
+        <v>1.8903</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.787500000000001</v>
+        <v>-5.8897</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.7737</v>
+        <v>-5.8657</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.3583</v>
+        <v>-5.7002</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.4155</v>
+        <v>-0.1655000000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.8332</v>
+        <v>-3.9379</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.5658</v>
+        <v>0.4704</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.267199999999999</v>
+        <v>-4.4082</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.5651</v>
+        <v>-1.4091</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5900999999999997</v>
+        <v>1.2725</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.975</v>
+        <v>-2.6816</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.2681</v>
+        <v>-2.5288</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.9757</v>
+        <v>-0.8021</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.2924</v>
+        <v>-1.7267</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0418</v>
+        <v>2.5527</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.9135</v>
+        <v>-3.7131</v>
       </c>
       <c r="R13" t="n">
-        <v>7.955</v>
+        <v>6.2658</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7197</v>
+        <v>-2.449</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9442</v>
+        <v>-0.5779000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7758</v>
+        <v>-1.8711</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.2625</v>
+        <v>-2.0316</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0641</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3266</v>
+        <v>-2.0316</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,145 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.6159</v>
+        <v>-9.9114</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.6321</v>
+        <v>-8.108499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.984500000000001</v>
+        <v>-1.803</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.651</v>
+        <v>-8.350999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-42.1347</v>
+        <v>-1.1856</v>
       </c>
       <c r="I14" t="n">
-        <v>28.4843</v>
+        <v>-7.1653</v>
       </c>
       <c r="J14" t="n">
-        <v>32.86099999999999</v>
+        <v>-3.7724</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.8835</v>
+        <v>1.0064</v>
       </c>
       <c r="L14" t="n">
-        <v>34.74400000000001</v>
+        <v>-4.778799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-46.5116</v>
+        <v>-4.5785</v>
       </c>
       <c r="N14" t="n">
-        <v>-40.2516</v>
+        <v>-2.192</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.2605</v>
+        <v>-2.3867</v>
       </c>
       <c r="P14" t="n">
-        <v>7.019499999999999</v>
+        <v>2.0887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-77.21149999999999</v>
+        <v>-5.3377</v>
       </c>
       <c r="R14" t="n">
-        <v>84.2299</v>
+        <v>7.426300000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.7886</v>
+        <v>-1.6518</v>
       </c>
       <c r="T14" t="n">
-        <v>6.752199999999998</v>
+        <v>-0.2116</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.5408</v>
+        <v>-1.4401</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.1969</v>
+        <v>-1.9974</v>
       </c>
       <c r="W14" t="n">
-        <v>29.9654</v>
+        <v>1.213</v>
       </c>
       <c r="X14" t="n">
-        <v>-35.1623</v>
+        <v>-3.2104</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Joventut Badalona</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-6.741300000000003</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-12.2197</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.477999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.935600000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-14.4619</v>
+      </c>
+      <c r="I15" t="n">
+        <v>20.3983</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.2163</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.7637</v>
+      </c>
+      <c r="L15" t="n">
+        <v>24.4529</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-27.28</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-23.2251</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-4.0553</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.641500000000001</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-83.54639999999999</v>
+      </c>
+      <c r="R15" t="n">
+        <v>88.1875</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-8.292</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.9653</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-15.2571</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-9.027200000000002</v>
+      </c>
+      <c r="W15" t="n">
+        <v>31.1445</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-40.1714</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -565,67 +565,67 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1752</v>
+        <v>12.191</v>
       </c>
       <c r="E2" t="n">
-        <v>5.611400000000001</v>
+        <v>5.3683</v>
       </c>
       <c r="F2" t="n">
-        <v>6.5637</v>
+        <v>6.8228</v>
       </c>
       <c r="G2" t="n">
-        <v>11.9554</v>
+        <v>11.9594</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0532</v>
+        <v>-0.9870999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>13.0085</v>
+        <v>12.9463</v>
       </c>
       <c r="J2" t="n">
-        <v>11.1984</v>
+        <v>10.9796</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8809</v>
+        <v>-0.9372999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>12.0793</v>
+        <v>11.9169</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7570999999999999</v>
+        <v>0.9796999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1722</v>
+        <v>-0.04960000000000003</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9293</v>
+        <v>1.0292</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.999999999987796e-05</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.266</v>
+        <v>-6.3116</v>
       </c>
       <c r="R2" t="n">
-        <v>6.2659</v>
+        <v>6.3117</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1077999999999998</v>
+        <v>0.1044000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001600000000000018</v>
+        <v>0.03270000000000012</v>
       </c>
       <c r="U2" t="n">
-        <v>0.106</v>
+        <v>0.0716</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1118999999999999</v>
+        <v>0.1272</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6772</v>
+        <v>0.6675</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5653</v>
+        <v>-0.5403</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>7.265400000000001</v>
+        <v>7.4425</v>
       </c>
       <c r="E3" t="n">
-        <v>6.161300000000001</v>
+        <v>5.9728</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1042</v>
+        <v>1.4697</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5377</v>
+        <v>1.6504</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5645</v>
+        <v>-1.5585</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1025</v>
+        <v>3.209</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3462</v>
+        <v>4.1382</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9818999999999998</v>
+        <v>0.8249</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3642</v>
+        <v>3.3129</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8082</v>
+        <v>-2.4877</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.5464</v>
+        <v>-2.3836</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2617999999999999</v>
+        <v>-0.1042</v>
       </c>
       <c r="P3" t="n">
-        <v>6.7301</v>
+        <v>6.7792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6246</v>
+        <v>-1.6364</v>
       </c>
       <c r="R3" t="n">
-        <v>8.354700000000001</v>
+        <v>8.4155</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2105000000000001</v>
+        <v>0.2129000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6191000000000001</v>
+        <v>0.6738</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4084</v>
+        <v>-0.4608999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.213</v>
+        <v>-1.1999</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8206</v>
+        <v>2.7975</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.0336</v>
+        <v>-3.9973</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0988</v>
+        <v>3.7494</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6126</v>
+        <v>0.823599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4861</v>
+        <v>2.9257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3716999999999997</v>
+        <v>0.1465999999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9353000000000002</v>
+        <v>0.7526999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5634999999999994</v>
+        <v>-0.6061000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3605</v>
+        <v>2.7355</v>
       </c>
       <c r="K4" t="n">
-        <v>4.559100000000001</v>
+        <v>4.1538</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1986</v>
+        <v>-1.4183</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9888</v>
+        <v>-2.5887</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.6238</v>
+        <v>-3.4012</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6351</v>
+        <v>0.8122999999999998</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.7848</v>
+        <v>-2.8052</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.4602</v>
+        <v>-13.5584</v>
       </c>
       <c r="R4" t="n">
-        <v>10.6753</v>
+        <v>10.7532</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.5198</v>
+        <v>-2.5455</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1355000000000001</v>
+        <v>-0.08329999999999993</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.3843</v>
+        <v>-2.462</v>
       </c>
       <c r="V4" t="n">
-        <v>9.031700000000001</v>
+        <v>8.953199999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>11.8479</v>
+        <v>11.7299</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.816</v>
+        <v>-2.7766</v>
       </c>
     </row>
     <row r="5">
@@ -799,28 +799,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5206</v>
+        <v>0.5153</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5206</v>
+        <v>0.5153</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5206</v>
+        <v>0.5153</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5206</v>
+        <v>0.5153</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5206</v>
+        <v>0.5153</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5206</v>
+        <v>0.5153</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3397</v>
+        <v>0.3506</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2053</v>
+        <v>-0.2175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.545</v>
+        <v>0.5682</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2625</v>
+        <v>-0.2636</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2165</v>
+        <v>-0.2274</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.046</v>
+        <v>-0.0363</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.175</v>
+        <v>-0.1894</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2118</v>
+        <v>-0.226</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0742</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0047</v>
+        <v>-0.0013</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0828</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9283</v>
+        <v>0.9351</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9283</v>
+        <v>0.9351</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1848</v>
+        <v>-0.1858</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0303</v>
+        <v>-0.0282</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1546</v>
+        <v>-0.1576</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1413</v>
+        <v>-0.1351</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1413</v>
+        <v>-0.1351</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08910000000000018</v>
+        <v>-0.07150000000000034</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06210000000000027</v>
+        <v>-0.1564999999999996</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1514</v>
+        <v>0.08509999999999995</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9427</v>
+        <v>4.929399999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4104</v>
+        <v>1.3374</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5323</v>
+        <v>3.5919</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4424</v>
+        <v>3.2593</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7198</v>
+        <v>0.5492000000000004</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7228</v>
+        <v>2.7101</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5004</v>
+        <v>1.67</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6908</v>
+        <v>0.7883</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8096000000000001</v>
+        <v>0.8817</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3925</v>
+        <v>1.4026</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.1773</v>
+        <v>-4.2079</v>
       </c>
       <c r="R7" t="n">
-        <v>5.569800000000001</v>
+        <v>5.6105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2768</v>
+        <v>-0.2839999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.1167</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3669999999999999</v>
+        <v>-0.4006999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.1477</v>
+        <v>-6.119400000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7066000000000001</v>
+        <v>0.6754</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.854200000000001</v>
+        <v>-6.7948</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1298999999999997</v>
+        <v>-0.2306000000000008</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9776</v>
+        <v>2.313999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1073</v>
+        <v>-2.5446</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2306</v>
+        <v>2.218</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1715</v>
+        <v>-4.230600000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4021</v>
+        <v>6.448399999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>10.7875</v>
+        <v>10.2305</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5159000000000002</v>
+        <v>0.1839</v>
       </c>
       <c r="L8" t="n">
-        <v>10.2717</v>
+        <v>10.0465</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.556900000000001</v>
+        <v>-8.012600000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.6873</v>
+        <v>-4.414499999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.8696</v>
+        <v>-3.598</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.481</v>
+        <v>-3.5066</v>
       </c>
       <c r="Q8" t="n">
-        <v>-15.0847</v>
+        <v>-15.1948</v>
       </c>
       <c r="R8" t="n">
-        <v>11.6036</v>
+        <v>11.6883</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.0885</v>
+        <v>-3.1031</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1378999999999999</v>
+        <v>0.2131999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.2264</v>
+        <v>-3.3163</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2091</v>
+        <v>4.161</v>
       </c>
       <c r="W8" t="n">
-        <v>7.136800000000001</v>
+        <v>7.0649</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9278</v>
+        <v>-2.9039</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5065</v>
+        <v>-1.4785</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0991</v>
+        <v>-3.2249</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5924</v>
+        <v>1.7464</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1064</v>
+        <v>-1.1054</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2090000000000001</v>
+        <v>0.2134</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3153</v>
+        <v>-1.3187</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.793</v>
+        <v>-1.9075</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3602</v>
+        <v>-0.4221</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4328</v>
+        <v>-1.4854</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6866000000000001</v>
+        <v>0.802</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5694</v>
+        <v>0.6354000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1173</v>
+        <v>0.1666</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3924</v>
+        <v>1.4026</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3208</v>
+        <v>-2.3376</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7132</v>
+        <v>3.7403</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6914</v>
+        <v>-0.7029000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.05689999999999998</v>
+        <v>-0.04469999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6582</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1012</v>
+        <v>-1.0728</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0717</v>
+        <v>1.0649</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1729</v>
+        <v>-2.1377</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1267</v>
+        <v>-3.0906</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.3322</v>
+        <v>-10.7385</v>
       </c>
       <c r="F10" t="n">
-        <v>7.2055</v>
+        <v>7.6482</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7852</v>
+        <v>3.851</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2922999999999999</v>
+        <v>0.3907</v>
       </c>
       <c r="I10" t="n">
-        <v>3.493</v>
+        <v>3.4604</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2667</v>
+        <v>1.9297</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7592</v>
+        <v>2.6334</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4926000000000004</v>
+        <v>-0.7038</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5185</v>
+        <v>1.9213</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.467</v>
+        <v>-2.2429</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9856</v>
+        <v>4.164</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.4093</v>
+        <v>-4.4415</v>
       </c>
       <c r="Q10" t="n">
-        <v>-15.3168</v>
+        <v>-15.4286</v>
       </c>
       <c r="R10" t="n">
-        <v>10.9075</v>
+        <v>10.987</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5008</v>
+        <v>-0.5051000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2221</v>
+        <v>1.2901</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7228</v>
+        <v>-1.7951</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.002</v>
+        <v>-1.9948</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4957</v>
+        <v>1.4701</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.4977</v>
+        <v>-3.4649</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6901</v>
+        <v>-4.662100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9852999999999998</v>
+        <v>-1.3156</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.705</v>
+        <v>-3.3465</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.792199999999999</v>
+        <v>-4.8332</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.641299999999999</v>
+        <v>-6.8161</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8492</v>
+        <v>1.9828</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3128</v>
+        <v>-1.6562</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.7712</v>
+        <v>-5.098700000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>3.4585</v>
+        <v>3.4426</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.4794</v>
+        <v>-3.1769</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8702</v>
+        <v>-1.7173</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6094</v>
+        <v>-1.4596</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4641000000000001</v>
+        <v>-0.4675</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.4263</v>
+        <v>-7.4805</v>
       </c>
       <c r="R11" t="n">
-        <v>6.962200000000001</v>
+        <v>7.0129</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3126</v>
+        <v>4.3451</v>
       </c>
       <c r="T11" t="n">
-        <v>5.4691</v>
+        <v>5.5562</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1565</v>
+        <v>-1.2111</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.7462</v>
+        <v>-3.7065</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2847</v>
+        <v>2.265</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.030900000000001</v>
+        <v>-5.9715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8216</v>
+        <v>-5.7943</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7347000000000001</v>
+        <v>-5.858000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0867</v>
+        <v>0.06390000000000007</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9582999999999999</v>
+        <v>-3.8896</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.467300000000001</v>
+        <v>0.5244</v>
       </c>
       <c r="I12" t="n">
-        <v>2.509</v>
+        <v>-4.4141</v>
       </c>
       <c r="J12" t="n">
-        <v>5.7563</v>
+        <v>-1.5608</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6524</v>
+        <v>1.2269</v>
       </c>
       <c r="L12" t="n">
-        <v>3.104</v>
+        <v>-2.7877</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.7146</v>
+        <v>-2.3288</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.119599999999999</v>
+        <v>-0.7026000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5952000000000001</v>
+        <v>-1.6262</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6960999999999999</v>
+        <v>2.5713</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.818900000000001</v>
+        <v>-3.7403</v>
       </c>
       <c r="R12" t="n">
-        <v>9.514900000000001</v>
+        <v>6.3116</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.56</v>
+        <v>-2.4734</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4374</v>
+        <v>-0.5569</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9973</v>
+        <v>-1.9165</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.9995</v>
+        <v>-2.0026</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8903</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.8897</v>
+        <v>-2.0026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8657</v>
+        <v>-5.8478</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7002</v>
+        <v>-1.2554</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1655000000000002</v>
+        <v>-4.5924</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.9379</v>
+        <v>-1.0092</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4704</v>
+        <v>-3.556299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.4082</v>
+        <v>2.5472</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4091</v>
+        <v>5.2553</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2725</v>
+        <v>2.3317</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6816</v>
+        <v>2.9238</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5288</v>
+        <v>-6.2644</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8021</v>
+        <v>-5.888</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7267</v>
+        <v>-0.3765999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5527</v>
+        <v>0.7013</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.7131</v>
+        <v>-8.883000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>6.2658</v>
+        <v>9.5844</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.449</v>
+        <v>-1.5711</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5779000000000001</v>
+        <v>0.5048000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8711</v>
+        <v>-2.076</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0316</v>
+        <v>-3.9687</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.8675</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0316</v>
+        <v>-5.8363</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.9114</v>
+        <v>-9.777200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.108499999999999</v>
+        <v>-8.312799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.803</v>
+        <v>-1.4645</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.350999999999999</v>
+        <v>-8.235100000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1856</v>
+        <v>-1.1311</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.1653</v>
+        <v>-7.104</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.7724</v>
+        <v>-3.9608</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0064</v>
+        <v>0.9144000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.778799999999999</v>
+        <v>-4.875299999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.5785</v>
+        <v>-4.2742</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.192</v>
+        <v>-2.0458</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.3867</v>
+        <v>-2.2286</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0887</v>
+        <v>2.1039</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.3377</v>
+        <v>-5.3766</v>
       </c>
       <c r="R14" t="n">
-        <v>7.426300000000001</v>
+        <v>7.4805</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6518</v>
+        <v>-1.6719</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2116</v>
+        <v>-0.1754</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4401</v>
+        <v>-1.4965</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9974</v>
+        <v>-1.974</v>
       </c>
       <c r="W14" t="n">
-        <v>1.213</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2104</v>
+        <v>-3.174</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.741300000000003</v>
+        <v>-6.703799999999997</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.2197</v>
+        <v>-16.0852</v>
       </c>
       <c r="F15" t="n">
-        <v>5.477999999999999</v>
+        <v>9.381999999999998</v>
       </c>
       <c r="G15" t="n">
-        <v>5.935600000000001</v>
+        <v>5.933999999999994</v>
       </c>
       <c r="H15" t="n">
-        <v>-14.4619</v>
+        <v>-14.7732</v>
       </c>
       <c r="I15" t="n">
-        <v>20.3983</v>
+        <v>20.7068</v>
       </c>
       <c r="J15" t="n">
-        <v>33.2163</v>
+        <v>29.7687</v>
       </c>
       <c r="K15" t="n">
-        <v>8.7637</v>
+        <v>6.6494</v>
       </c>
       <c r="L15" t="n">
-        <v>24.4529</v>
+        <v>23.1189</v>
       </c>
       <c r="M15" t="n">
-        <v>-27.28</v>
+        <v>-23.8345</v>
       </c>
       <c r="N15" t="n">
-        <v>-23.2251</v>
+        <v>-21.4231</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.0553</v>
+        <v>-2.4123</v>
       </c>
       <c r="P15" t="n">
-        <v>4.641500000000001</v>
+        <v>4.6751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-83.54639999999999</v>
+        <v>-84.15570000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>88.1875</v>
+        <v>88.831</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.292</v>
+        <v>-8.380400000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>6.9653</v>
+        <v>7.499000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-15.2571</v>
+        <v>-15.8793</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.027200000000002</v>
+        <v>-8.932400000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>31.1445</v>
+        <v>30.8027</v>
       </c>
       <c r="X15" t="n">
-        <v>-40.1714</v>
+        <v>-39.735</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -565,67 +565,67 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>12.191</v>
+        <v>12.1897</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3683</v>
+        <v>5.338200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8228</v>
+        <v>6.851400000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>11.9594</v>
+        <v>11.9518</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9870999999999999</v>
+        <v>-0.9884000000000002</v>
       </c>
       <c r="I2" t="n">
-        <v>12.9463</v>
+        <v>12.94</v>
       </c>
       <c r="J2" t="n">
-        <v>10.9796</v>
+        <v>10.9882</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9372999999999999</v>
+        <v>-0.9335</v>
       </c>
       <c r="L2" t="n">
-        <v>11.9169</v>
+        <v>11.9218</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9796999999999999</v>
+        <v>0.9637000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.04960000000000003</v>
+        <v>-0.05470000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0292</v>
+        <v>1.0184</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.3116</v>
+        <v>-6.3165</v>
       </c>
       <c r="R2" t="n">
-        <v>6.3117</v>
+        <v>6.316599999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1044000000000001</v>
+        <v>0.1089000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03270000000000012</v>
+        <v>0.0001999999999999086</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0716</v>
+        <v>0.1087</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1272</v>
+        <v>0.1288999999999998</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6675</v>
+        <v>0.6665000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5403</v>
+        <v>-0.5376</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4425</v>
+        <v>7.436900000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9728</v>
+        <v>5.9241</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4697</v>
+        <v>1.5128</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6504</v>
+        <v>1.6388</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5585</v>
+        <v>-1.5564</v>
       </c>
       <c r="I3" t="n">
-        <v>3.209</v>
+        <v>3.1954</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1382</v>
+        <v>4.1455</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8249</v>
+        <v>0.8304</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3129</v>
+        <v>3.3151</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4877</v>
+        <v>-2.5065</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3836</v>
+        <v>-2.3868</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1042</v>
+        <v>-0.1197000000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>6.7792</v>
+        <v>6.7843</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6364</v>
+        <v>-1.6375</v>
       </c>
       <c r="R3" t="n">
-        <v>8.4155</v>
+        <v>8.4221</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2129000000000001</v>
+        <v>0.2122</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6738</v>
+        <v>0.6214999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4608999999999999</v>
+        <v>-0.4092</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1999</v>
+        <v>-1.1986</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7975</v>
+        <v>2.7949</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.9973</v>
+        <v>-3.9935</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7494</v>
+        <v>3.755399999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.823599999999999</v>
+        <v>0.7783000000000007</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9257</v>
+        <v>2.9772</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1465999999999998</v>
+        <v>0.1580000000000008</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7526999999999999</v>
+        <v>0.7591999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6061000000000001</v>
+        <v>-0.6011999999999995</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7355</v>
+        <v>2.7694</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1538</v>
+        <v>4.164400000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4183</v>
+        <v>-1.3951</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5887</v>
+        <v>-2.6113</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.4012</v>
+        <v>-3.4053</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8122999999999998</v>
+        <v>0.794</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.8052</v>
+        <v>-2.8074</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.5584</v>
+        <v>-13.5689</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7532</v>
+        <v>10.7616</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.5455</v>
+        <v>-2.54</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08329999999999993</v>
+        <v>-0.1393</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.462</v>
+        <v>-2.4008</v>
       </c>
       <c r="V4" t="n">
-        <v>8.953199999999999</v>
+        <v>8.944800000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>11.7299</v>
+        <v>11.7172</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7766</v>
+        <v>-2.7724</v>
       </c>
     </row>
     <row r="5">
@@ -799,28 +799,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5153</v>
+        <v>0.5148</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5153</v>
+        <v>0.5148</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5153</v>
+        <v>0.5148</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5153</v>
+        <v>0.5148</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5153</v>
+        <v>0.5148</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5153</v>
+        <v>0.5148</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3506</v>
+        <v>0.3513</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2175</v>
+        <v>-0.2191</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5682</v>
+        <v>0.5704</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2636</v>
+        <v>-0.2638</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2274</v>
+        <v>-0.2266</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0363</v>
+        <v>-0.0372</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1894</v>
+        <v>-0.1885</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.226</v>
+        <v>-0.2251</v>
       </c>
       <c r="L6" t="n">
         <v>0.0366</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0742</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0013</v>
+        <v>-0.0015</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0738</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9351</v>
+        <v>0.9358</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9351</v>
+        <v>0.9358</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1858</v>
+        <v>-0.1863</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0282</v>
+        <v>-0.0306</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1576</v>
+        <v>-0.1557</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1351</v>
+        <v>-0.1344</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1351</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07150000000000034</v>
+        <v>-0.07050000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1564999999999996</v>
+        <v>-0.1852</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08509999999999995</v>
+        <v>0.1146</v>
       </c>
       <c r="G7" t="n">
-        <v>4.929399999999999</v>
+        <v>4.920999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3374</v>
+        <v>1.3385</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5919</v>
+        <v>3.5825</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2593</v>
+        <v>3.2642</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5492000000000004</v>
+        <v>0.5553999999999998</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7101</v>
+        <v>2.7088</v>
       </c>
       <c r="M7" t="n">
-        <v>1.67</v>
+        <v>1.6567</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7883</v>
+        <v>0.7828999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8817</v>
+        <v>0.8736999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4026</v>
+        <v>1.4036</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.2079</v>
+        <v>-4.211</v>
       </c>
       <c r="R7" t="n">
-        <v>5.6105</v>
+        <v>5.6145</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2839999999999999</v>
+        <v>-0.2787000000000002</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1167</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4006999999999999</v>
+        <v>-0.3685</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.119400000000001</v>
+        <v>-6.116400000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6754</v>
+        <v>0.6720000000000002</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.7948</v>
+        <v>-6.7884</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2306000000000008</v>
+        <v>-0.2511999999999994</v>
       </c>
       <c r="E8" t="n">
-        <v>2.313999999999999</v>
+        <v>2.242499999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5446</v>
+        <v>-2.4938</v>
       </c>
       <c r="G8" t="n">
-        <v>2.218</v>
+        <v>2.216</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.230600000000001</v>
+        <v>-4.2218</v>
       </c>
       <c r="I8" t="n">
-        <v>6.448399999999999</v>
+        <v>6.4377</v>
       </c>
       <c r="J8" t="n">
-        <v>10.2305</v>
+        <v>10.2569</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1839</v>
+        <v>0.1975999999999996</v>
       </c>
       <c r="L8" t="n">
-        <v>10.0465</v>
+        <v>10.0594</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.012600000000001</v>
+        <v>-8.040900000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.414499999999999</v>
+        <v>-4.4193</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.598</v>
+        <v>-3.6216</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.5066</v>
+        <v>-3.5093</v>
       </c>
       <c r="Q8" t="n">
-        <v>-15.1948</v>
+        <v>-15.2066</v>
       </c>
       <c r="R8" t="n">
-        <v>11.6883</v>
+        <v>11.6974</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.1031</v>
+        <v>-3.1139</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2131999999999999</v>
+        <v>0.1349999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.3163</v>
+        <v>-3.2491</v>
       </c>
       <c r="V8" t="n">
-        <v>4.161</v>
+        <v>4.1559</v>
       </c>
       <c r="W8" t="n">
-        <v>7.0649</v>
+        <v>7.0572</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9039</v>
+        <v>-2.9013</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4785</v>
+        <v>-1.467</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2249</v>
+        <v>-3.2307</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7464</v>
+        <v>1.764</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1054</v>
+        <v>-1.1043</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2134</v>
+        <v>0.2129</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3187</v>
+        <v>-1.3172</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9075</v>
+        <v>-1.8976</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4221</v>
+        <v>-0.4188</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4854</v>
+        <v>-1.4788</v>
       </c>
       <c r="M9" t="n">
-        <v>0.802</v>
+        <v>0.7932</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6354000000000001</v>
+        <v>0.6317</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1666</v>
+        <v>0.1617</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4026</v>
+        <v>1.4036</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3376</v>
+        <v>-2.3394</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7403</v>
+        <v>3.743</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7029000000000001</v>
+        <v>-0.6967</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.04469999999999999</v>
+        <v>-0.05809999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6582</v>
+        <v>-0.6386999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0728</v>
+        <v>-1.0697</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1377</v>
+        <v>-2.1339</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0906</v>
+        <v>-3.0975</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.7385</v>
+        <v>-10.7915</v>
       </c>
       <c r="F10" t="n">
-        <v>7.6482</v>
+        <v>7.694</v>
       </c>
       <c r="G10" t="n">
-        <v>3.851</v>
+        <v>3.8462</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3907</v>
+        <v>0.3856999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4604</v>
+        <v>3.4603</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9297</v>
+        <v>1.9528</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6334</v>
+        <v>2.6347</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7038</v>
+        <v>-0.6819</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9213</v>
+        <v>1.8934</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2429</v>
+        <v>-2.249</v>
       </c>
       <c r="O10" t="n">
-        <v>4.164</v>
+        <v>4.1422</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.4415</v>
+        <v>-4.4451</v>
       </c>
       <c r="Q10" t="n">
-        <v>-15.4286</v>
+        <v>-15.4405</v>
       </c>
       <c r="R10" t="n">
-        <v>10.987</v>
+        <v>10.9956</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5051000000000001</v>
+        <v>-0.5047000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2901</v>
+        <v>1.2289</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7951</v>
+        <v>-1.7336</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.9948</v>
+        <v>-1.994</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4701</v>
+        <v>1.4674</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.4649</v>
+        <v>-3.4614</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.662100000000001</v>
+        <v>-4.6534</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3156</v>
+        <v>-1.3489</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3465</v>
+        <v>-3.3044</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8332</v>
+        <v>-4.830799999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.8161</v>
+        <v>-6.798299999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9828</v>
+        <v>1.9677</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6562</v>
+        <v>-1.6363</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.098700000000001</v>
+        <v>-5.077299999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>3.4426</v>
+        <v>3.4408</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1769</v>
+        <v>-3.1944</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7173</v>
+        <v>-1.7213</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4596</v>
+        <v>-1.4732</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4675</v>
+        <v>-0.4678</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.4805</v>
+        <v>-7.4863</v>
       </c>
       <c r="R11" t="n">
-        <v>7.0129</v>
+        <v>7.0183</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3451</v>
+        <v>4.3473</v>
       </c>
       <c r="T11" t="n">
-        <v>5.5562</v>
+        <v>5.511</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2111</v>
+        <v>-1.1636</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.7065</v>
+        <v>-3.7022</v>
       </c>
       <c r="W11" t="n">
-        <v>2.265</v>
+        <v>2.2628</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.9715</v>
+        <v>-5.965000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7943</v>
+        <v>-5.7826</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.858000000000001</v>
+        <v>-5.8746</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06390000000000007</v>
+        <v>0.09209999999999996</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8896</v>
+        <v>-3.8878</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5244</v>
+        <v>0.5214</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4141</v>
+        <v>-4.4092</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5608</v>
+        <v>-1.5476</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2269</v>
+        <v>1.227</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7877</v>
+        <v>-2.7745</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3288</v>
+        <v>-2.3403</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7026000000000001</v>
+        <v>-0.7055999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6262</v>
+        <v>-1.6347</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5713</v>
+        <v>2.5735</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.7403</v>
+        <v>-3.7432</v>
       </c>
       <c r="R12" t="n">
-        <v>6.3116</v>
+        <v>6.316599999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4734</v>
+        <v>-2.4686</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5569</v>
+        <v>-0.5837999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9165</v>
+        <v>-1.8847</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0026</v>
+        <v>-1.9995</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.0026</v>
+        <v>-1.9995</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8478</v>
+        <v>-5.8426</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2554</v>
+        <v>-1.307</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.5924</v>
+        <v>-4.5357</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0092</v>
+        <v>-1.0064</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.556299999999999</v>
+        <v>-3.5471</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5472</v>
+        <v>2.540900000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2553</v>
+        <v>5.2804</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3317</v>
+        <v>2.3414</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9238</v>
+        <v>2.9389</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.2644</v>
+        <v>-6.2867</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.888</v>
+        <v>-5.888500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3765999999999999</v>
+        <v>-0.398</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7013</v>
+        <v>0.7018</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.883000000000001</v>
+        <v>-8.889799999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>9.5844</v>
+        <v>9.591799999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5711</v>
+        <v>-1.5727</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5048000000000001</v>
+        <v>0.4375999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.076</v>
+        <v>-2.0103</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.9687</v>
+        <v>-3.9655</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8675</v>
+        <v>1.8651</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.8363</v>
+        <v>-5.8306</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.777200000000001</v>
+        <v>-9.765599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.312799999999999</v>
+        <v>-8.3414</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4645</v>
+        <v>-1.4242</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.235100000000001</v>
+        <v>-8.234999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1311</v>
+        <v>-1.1318</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.104</v>
+        <v>-7.1032</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.9608</v>
+        <v>-3.9439</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9144000000000001</v>
+        <v>0.917</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.875299999999999</v>
+        <v>-4.8611</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.2742</v>
+        <v>-4.291</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0458</v>
+        <v>-2.0488</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2286</v>
+        <v>-2.2421</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1039</v>
+        <v>2.1055</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.3766</v>
+        <v>-5.3807</v>
       </c>
       <c r="R14" t="n">
-        <v>7.4805</v>
+        <v>7.4862</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6719</v>
+        <v>-1.6647</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1754</v>
+        <v>-0.2153</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4965</v>
+        <v>-1.4494</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.974</v>
+        <v>-1.9715</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.1986</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.174</v>
+        <v>-3.1701</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.703799999999997</v>
+        <v>-6.682300000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.0852</v>
+        <v>-16.5005</v>
       </c>
       <c r="F15" t="n">
-        <v>9.381999999999998</v>
+        <v>9.8184</v>
       </c>
       <c r="G15" t="n">
-        <v>5.933999999999994</v>
+        <v>5.9185</v>
       </c>
       <c r="H15" t="n">
-        <v>-14.7732</v>
+        <v>-14.7379</v>
       </c>
       <c r="I15" t="n">
-        <v>20.7068</v>
+        <v>20.6565</v>
       </c>
       <c r="J15" t="n">
-        <v>29.7687</v>
+        <v>29.9583</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6494</v>
+        <v>6.728000000000002</v>
       </c>
       <c r="L15" t="n">
-        <v>23.1189</v>
+        <v>23.23</v>
       </c>
       <c r="M15" t="n">
-        <v>-23.8345</v>
+        <v>-24.0394</v>
       </c>
       <c r="N15" t="n">
-        <v>-21.4231</v>
+        <v>-21.4662</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.4123</v>
+        <v>-2.5731</v>
       </c>
       <c r="P15" t="n">
-        <v>4.6751</v>
+        <v>4.6785</v>
       </c>
       <c r="Q15" t="n">
-        <v>-84.15570000000001</v>
+        <v>-84.2204</v>
       </c>
       <c r="R15" t="n">
-        <v>88.831</v>
+        <v>88.89949999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.380400000000002</v>
+        <v>-8.357900000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>7.499000000000001</v>
+        <v>6.9967</v>
       </c>
       <c r="U15" t="n">
-        <v>-15.8793</v>
+        <v>-15.3549</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.932400000000001</v>
+        <v>-8.922200000000002</v>
       </c>
       <c r="W15" t="n">
-        <v>30.8027</v>
+        <v>30.7659</v>
       </c>
       <c r="X15" t="n">
-        <v>-39.735</v>
+        <v>-39.6881</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total_NP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Off_NP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Def_NP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Net_Shooting</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Net_2P</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_3P</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Off_Shooting</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Off_2P</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Off_3P</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Def_Shooting</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Def_2P</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Def_3P</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Net_TOV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Off_TOV</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Def_TOV</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Net_ORB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Off_ORB</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Def_ORB</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Net_FT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Off_FT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Def_FT</t>
         </is>
@@ -565,67 +553,67 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1897</v>
+        <v>12.1892</v>
       </c>
       <c r="E2" t="n">
-        <v>5.338200000000001</v>
+        <v>5.3354</v>
       </c>
       <c r="F2" t="n">
-        <v>6.851400000000001</v>
+        <v>6.853800000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>11.9518</v>
+        <v>11.9503</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9884000000000002</v>
+        <v>-0.9892000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>12.94</v>
+        <v>12.9397</v>
       </c>
       <c r="J2" t="n">
-        <v>10.9882</v>
+        <v>10.9926</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9335</v>
+        <v>-0.9319999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>11.9218</v>
+        <v>11.9247</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9637000000000002</v>
+        <v>0.9577999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.05470000000000001</v>
+        <v>-0.05729999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0184</v>
+        <v>1.015</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.3165</v>
+        <v>-6.317</v>
       </c>
       <c r="R2" t="n">
-        <v>6.316599999999999</v>
+        <v>6.3171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1089000000000001</v>
+        <v>0.1098</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0001999999999999086</v>
+        <v>-0.006500000000000047</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1087</v>
+        <v>0.1164999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1288999999999998</v>
+        <v>0.1291</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6665000000000001</v>
+        <v>0.6664000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5376</v>
+        <v>-0.5372</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +631,67 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>7.436900000000001</v>
+        <v>7.4336</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9241</v>
+        <v>5.9168</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5128</v>
+        <v>1.5166</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6388</v>
+        <v>1.6352</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5564</v>
+        <v>-1.5561</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1954</v>
+        <v>3.1913</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1455</v>
+        <v>4.1494</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8304</v>
+        <v>0.8333999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3151</v>
+        <v>3.316</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5065</v>
+        <v>-2.5142</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3868</v>
+        <v>-2.3894</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1197000000000002</v>
+        <v>-0.1246</v>
       </c>
       <c r="P3" t="n">
-        <v>6.7843</v>
+        <v>6.784899999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6375</v>
+        <v>-1.6378</v>
       </c>
       <c r="R3" t="n">
-        <v>8.4221</v>
+        <v>8.422699999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2122</v>
+        <v>0.2119999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6214999999999999</v>
+        <v>0.6106</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4092</v>
+        <v>-0.3986</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1986</v>
+        <v>-1.1984</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7949</v>
+        <v>2.7947</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.9935</v>
+        <v>-3.993</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +709,67 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.755399999999999</v>
+        <v>3.7608</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7783000000000007</v>
+        <v>0.7791999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9772</v>
+        <v>2.9816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1580000000000008</v>
+        <v>0.1630000000000003</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7591999999999999</v>
+        <v>0.7626999999999997</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6011999999999995</v>
+        <v>-0.5996999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7694</v>
+        <v>2.783799999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>4.164400000000001</v>
+        <v>4.1715</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3951</v>
+        <v>-1.3877</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6113</v>
+        <v>-2.6207</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.4053</v>
+        <v>-3.4088</v>
       </c>
       <c r="O4" t="n">
-        <v>0.794</v>
+        <v>0.7882</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.8074</v>
+        <v>-2.8076</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.5689</v>
+        <v>-13.5698</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7616</v>
+        <v>10.7624</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.54</v>
+        <v>-2.5386</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1393</v>
+        <v>-0.1506999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.4008</v>
+        <v>-2.3878</v>
       </c>
       <c r="V4" t="n">
-        <v>8.944800000000001</v>
+        <v>8.944099999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>11.7172</v>
+        <v>11.7162</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7724</v>
+        <v>-2.772</v>
       </c>
     </row>
     <row r="5">
@@ -799,28 +787,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5148</v>
+        <v>0.5147</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5148</v>
+        <v>0.5147</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5148</v>
+        <v>0.5147</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5148</v>
+        <v>0.5147</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5148</v>
+        <v>0.5147</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5148</v>
+        <v>0.5147</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -880,64 +868,64 @@
         <v>0.3513</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2191</v>
+        <v>-0.2193</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5704</v>
+        <v>0.5706</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2638</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2266</v>
+        <v>-0.2263</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0372</v>
+        <v>-0.0375</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1885</v>
+        <v>-0.1881</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2251</v>
+        <v>-0.2247</v>
       </c>
       <c r="L6" t="n">
         <v>0.0366</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0757</v>
       </c>
       <c r="N6" t="n">
         <v>-0.0015</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0738</v>
+        <v>-0.0741</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9358</v>
+        <v>0.9359</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9358</v>
+        <v>0.9359</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1863</v>
+        <v>-0.1865</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0306</v>
+        <v>-0.0312</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1557</v>
+        <v>-0.1553</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1344</v>
+        <v>-0.1343</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1344</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +943,67 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07050000000000001</v>
+        <v>-0.0708000000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1852</v>
+        <v>-0.1881000000000003</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1146</v>
+        <v>0.1174000000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>4.920999999999999</v>
+        <v>4.9194</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3385</v>
+        <v>1.3396</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5825</v>
+        <v>3.5799</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2642</v>
+        <v>3.2675</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5553999999999998</v>
+        <v>0.5588000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7088</v>
+        <v>2.7086</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6567</v>
+        <v>1.6519</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7828999999999999</v>
+        <v>0.7808</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8736999999999999</v>
+        <v>0.8713</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4036</v>
+        <v>1.4039</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.211</v>
+        <v>-4.2114</v>
       </c>
       <c r="R7" t="n">
-        <v>5.6145</v>
+        <v>5.6151</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2787000000000002</v>
+        <v>-0.2776999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08960000000000001</v>
+        <v>0.08409999999999995</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3685</v>
+        <v>-0.3618000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.116400000000001</v>
+        <v>-6.1163</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6720000000000002</v>
+        <v>0.6716</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.7884</v>
+        <v>-6.7879</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1021,67 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2511999999999994</v>
+        <v>-0.2539000000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>2.242499999999999</v>
+        <v>2.237000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4938</v>
+        <v>-2.4909</v>
       </c>
       <c r="G8" t="n">
-        <v>2.216</v>
+        <v>2.2159</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.2218</v>
+        <v>-4.2193</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4377</v>
+        <v>6.434900000000002</v>
       </c>
       <c r="J8" t="n">
-        <v>10.2569</v>
+        <v>10.269</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1975999999999996</v>
+        <v>0.2042999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>10.0594</v>
+        <v>10.0645</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.040900000000001</v>
+        <v>-8.0533</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.4193</v>
+        <v>-4.4236</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.6216</v>
+        <v>-3.6296</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.5093</v>
+        <v>-3.5095</v>
       </c>
       <c r="Q8" t="n">
-        <v>-15.2066</v>
+        <v>-15.2075</v>
       </c>
       <c r="R8" t="n">
-        <v>11.6974</v>
+        <v>11.6981</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.1139</v>
+        <v>-3.1158</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1349999999999999</v>
+        <v>0.1191000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.2491</v>
+        <v>-3.235</v>
       </c>
       <c r="V8" t="n">
-        <v>4.1559</v>
+        <v>4.1554</v>
       </c>
       <c r="W8" t="n">
-        <v>7.0572</v>
+        <v>7.0565</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9013</v>
+        <v>-2.901</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1099,67 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.467</v>
+        <v>-1.4649</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2307</v>
+        <v>-3.2304</v>
       </c>
       <c r="F9" t="n">
-        <v>1.764</v>
+        <v>1.7654</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1043</v>
+        <v>-1.1041</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2129</v>
+        <v>0.2128000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3172</v>
+        <v>-1.3169</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8976</v>
+        <v>-1.8941</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4188</v>
+        <v>-0.4174</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4788</v>
+        <v>-1.4768</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7932</v>
+        <v>0.7901</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6317</v>
+        <v>0.6301</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1617</v>
+        <v>0.1599</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4036</v>
+        <v>1.4037</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3394</v>
+        <v>-2.3396</v>
       </c>
       <c r="R9" t="n">
-        <v>3.743</v>
+        <v>3.7434</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6967</v>
+        <v>-0.6953</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.05809999999999998</v>
+        <v>-0.06070000000000002</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6386999999999999</v>
+        <v>-0.6344999999999998</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0697</v>
+        <v>-1.0694</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1339</v>
+        <v>-2.1335</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1177,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0975</v>
+        <v>-3.0993</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.7915</v>
+        <v>-10.7967</v>
       </c>
       <c r="F10" t="n">
-        <v>7.694</v>
+        <v>7.6975</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8462</v>
+        <v>3.8445</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3856999999999999</v>
+        <v>0.3838999999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4603</v>
+        <v>3.4606</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9528</v>
+        <v>1.9613</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6347</v>
+        <v>2.6365</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6819</v>
+        <v>-0.6753</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8934</v>
+        <v>1.883</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.249</v>
+        <v>-2.2528</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1422</v>
+        <v>4.1358</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.4451</v>
+        <v>-4.4454</v>
       </c>
       <c r="Q10" t="n">
-        <v>-15.4405</v>
+        <v>-15.4414</v>
       </c>
       <c r="R10" t="n">
-        <v>10.9956</v>
+        <v>10.9964</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5047000000000001</v>
+        <v>-0.5044000000000003</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2289</v>
+        <v>1.2163</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7336</v>
+        <v>-1.7208</v>
       </c>
       <c r="V10" t="n">
         <v>-1.994</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4674</v>
+        <v>1.4671</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.4614</v>
+        <v>-3.461</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1255,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6534</v>
+        <v>-4.652</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3489</v>
+        <v>-1.3515</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3044</v>
+        <v>-3.3006</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.830799999999999</v>
+        <v>-4.829599999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.798299999999999</v>
+        <v>-6.7927</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9677</v>
+        <v>1.9631</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6363</v>
+        <v>-1.6281</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.077299999999999</v>
+        <v>-5.069</v>
       </c>
       <c r="L11" t="n">
-        <v>3.4408</v>
+        <v>3.4407</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1944</v>
+        <v>-3.2014</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7213</v>
+        <v>-1.7236</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4732</v>
+        <v>-1.4776</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4678</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.4863</v>
+        <v>-7.4868</v>
       </c>
       <c r="R11" t="n">
-        <v>7.0183</v>
+        <v>7.018899999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3473</v>
+        <v>4.347399999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>5.511</v>
+        <v>5.5012</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1636</v>
+        <v>-1.1535</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.7022</v>
+        <v>-3.7018</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2628</v>
+        <v>2.2626</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.965000000000001</v>
+        <v>-5.9645</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1333,67 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7826</v>
+        <v>-5.7812</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8746</v>
+        <v>-5.876</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09209999999999996</v>
+        <v>0.0948</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8878</v>
+        <v>-3.888199999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5214</v>
+        <v>0.5201</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4092</v>
+        <v>-4.4082</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5476</v>
+        <v>-1.543</v>
       </c>
       <c r="K12" t="n">
-        <v>1.227</v>
+        <v>1.2275</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7745</v>
+        <v>-2.7705</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3403</v>
+        <v>-2.3451</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7055999999999999</v>
+        <v>-0.7073999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6347</v>
+        <v>-1.6377</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5735</v>
+        <v>2.5736</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.7432</v>
+        <v>-3.7434</v>
       </c>
       <c r="R12" t="n">
-        <v>6.316599999999999</v>
+        <v>6.317</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4686</v>
+        <v>-2.4674</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5837999999999999</v>
+        <v>-0.5893</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8847</v>
+        <v>-1.8779</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9995</v>
+        <v>-1.9992</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.9995</v>
+        <v>-1.9992</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1411,67 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8426</v>
+        <v>-5.841399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.307</v>
+        <v>-1.3104</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.5357</v>
+        <v>-4.5307</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0064</v>
+        <v>-1.0051</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.5471</v>
+        <v>-3.544300000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.540900000000001</v>
+        <v>2.5392</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2804</v>
+        <v>5.2915</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3414</v>
+        <v>2.3474</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9389</v>
+        <v>2.9442</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.2867</v>
+        <v>-6.296600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.888500000000001</v>
+        <v>-5.8917</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.398</v>
+        <v>-0.4047999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7018</v>
+        <v>0.7019</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.889799999999999</v>
+        <v>-8.890499999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>9.591799999999999</v>
+        <v>9.592499999999999</v>
       </c>
       <c r="S13" t="n">
         <v>-1.5727</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4375999999999999</v>
+        <v>0.4235999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0103</v>
+        <v>-1.9965</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.9655</v>
+        <v>-3.9652</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8651</v>
+        <v>1.8648</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.8306</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1489,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.765599999999999</v>
+        <v>-9.765000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.3414</v>
+        <v>-8.3444</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4242</v>
+        <v>-1.4206</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.234999999999999</v>
+        <v>-8.236499999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1318</v>
+        <v>-1.1325</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.1032</v>
+        <v>-7.1038</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.9439</v>
+        <v>-3.9385</v>
       </c>
       <c r="K14" t="n">
-        <v>0.917</v>
+        <v>0.9185999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.8611</v>
+        <v>-4.857</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.291</v>
+        <v>-4.2979</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0488</v>
+        <v>-2.0513</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2421</v>
+        <v>-2.2467</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1055</v>
+        <v>2.1057</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.3807</v>
+        <v>-5.3812</v>
       </c>
       <c r="R14" t="n">
-        <v>7.4862</v>
+        <v>7.4869</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6647</v>
+        <v>-1.6631</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2153</v>
+        <v>-0.2235</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4494</v>
+        <v>-1.4397</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9715</v>
+        <v>-1.9712</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1986</v>
+        <v>1.1984</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1701</v>
+        <v>-3.1696</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1567,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.682300000000001</v>
+        <v>-6.678900000000007</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.5005</v>
+        <v>-16.5337</v>
       </c>
       <c r="F15" t="n">
-        <v>9.8184</v>
+        <v>9.854900000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9185</v>
+        <v>5.915700000000005</v>
       </c>
       <c r="H15" t="n">
-        <v>-14.7379</v>
+        <v>-14.7266</v>
       </c>
       <c r="I15" t="n">
-        <v>20.6565</v>
+        <v>20.6426</v>
       </c>
       <c r="J15" t="n">
-        <v>29.9583</v>
+        <v>30.038</v>
       </c>
       <c r="K15" t="n">
-        <v>6.728000000000002</v>
+        <v>6.769599999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>23.23</v>
+        <v>23.268</v>
       </c>
       <c r="M15" t="n">
-        <v>-24.0394</v>
+        <v>-24.1221</v>
       </c>
       <c r="N15" t="n">
-        <v>-21.4662</v>
+        <v>-21.4965</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5731</v>
+        <v>-2.624900000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>4.6785</v>
+        <v>4.679199999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-84.2204</v>
+        <v>-84.22639999999998</v>
       </c>
       <c r="R15" t="n">
-        <v>88.89949999999999</v>
+        <v>88.9064</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.357900000000001</v>
+        <v>-8.352300000000003</v>
       </c>
       <c r="T15" t="n">
-        <v>6.9967</v>
+        <v>6.893000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-15.3549</v>
+        <v>-15.2449</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.922200000000002</v>
+        <v>-8.921200000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>30.7659</v>
+        <v>30.7624</v>
       </c>
       <c r="X15" t="n">
-        <v>-39.6881</v>
+        <v>-39.68320000000001</v>
       </c>
     </row>
   </sheetData>
